--- a/lineup-template.xlsx
+++ b/lineup-template.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns4="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:ns5="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:ns6="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:ns7="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:ns8="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:ns9="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" ns1:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30408"/>
   <workbookPr codeName="ThisWorkbook"/>
-  <ns1:AlternateContent>
-    <ns1:Choice Requires="x15">
-      <ns2:absPath url="https://marriottonline-my.sharepoint.com/personal/csard122_marriott_com/Documents/HSKP 2025/"/>
-    </ns1:Choice>
-  </ns1:AlternateContent>
-  <ns3:revisionPtr revIDLastSave="46706" documentId="13_ncr:1_{98CF7EA1-A6ED-48C7-BD3E-CCA19375D598}" ns4:coauthVersionLast="47" ns4:coauthVersionMax="47" ns5:uidLastSave="{DA498B0F-D18C-4BC9-8E17-97989716BCD7}"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url=""/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="46772" documentId="13_ncr:1_{98CF7EA1-A6ED-48C7-BD3E-CCA19375D598}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{073BB23C-AC0C-463C-A25F-82E96768433D}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" ns6:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="ACTUAL (new template )" sheetId="4" ns7:id="rId1"/>
-    <sheet name="TEST 1" sheetId="2" ns7:id="rId2"/>
-    <sheet name="TEST 2" sheetId="3" ns7:id="rId3"/>
-    <sheet name="ACTUAL" sheetId="1" ns7:id="rId4"/>
+    <sheet name="ACTUAL (new template )" sheetId="4" r:id="rId1"/>
+    <sheet name="TEST 1" sheetId="2" r:id="rId2"/>
+    <sheet name="TEST 2" sheetId="3" r:id="rId3"/>
+    <sheet name="ACTUAL" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">ACTUAL!$C$34:$E$45</definedName>
@@ -24,28 +24,28 @@
     <definedName name="_xlnm.Print_Area" localSheetId="3">ACTUAL!$A$1:$L$62</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'ACTUAL (new template )'!$A$1:$K$62</definedName>
   </definedNames>
-  <calcPr calcId="191028" calcCompleted="0" fullCalcOnLoad="1"/>
+  <calcPr calcId="191028"/>
   <extLst>
-    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <ns8:workbookPr chartTrackingRefBase="1"/>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <ns9:calcFeatures>
-        <ns9:feature name="microsoft.com:RD"/>
-        <ns9:feature name="microsoft.com:Single"/>
-        <ns9:feature name="microsoft.com:FV"/>
-        <ns9:feature name="microsoft.com:CNMTM"/>
-        <ns9:feature name="microsoft.com:LET_WF"/>
-        <ns9:feature name="microsoft.com:LAMBDA_WF"/>
-        <ns9:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </ns9:calcFeatures>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="147">
   <si>
     <t>HOUSEKEEPING</t>
   </si>
@@ -65,6 +65,9 @@
     <t>Day:</t>
   </si>
   <si>
+    <t xml:space="preserve">Saturday </t>
+  </si>
+  <si>
     <t xml:space="preserve">Notes </t>
   </si>
   <si>
@@ -74,6 +77,9 @@
     <t>Date:</t>
   </si>
   <si>
+    <t/>
+  </si>
+  <si>
     <t xml:space="preserve">PASS ONS:  </t>
   </si>
   <si>
@@ -86,6 +92,12 @@
     <t>Coordinator:</t>
   </si>
   <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
     <t>Floor Supervisors:</t>
   </si>
   <si>
@@ -95,45 +107,75 @@
     <t>Floor Supervisors PM:</t>
   </si>
   <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
     <t>AM Lobby</t>
   </si>
   <si>
+    <t/>
+  </si>
+  <si>
     <t xml:space="preserve">PM Lobby </t>
   </si>
   <si>
+    <t/>
+  </si>
+  <si>
     <t>House Attendants:</t>
   </si>
   <si>
+    <t xml:space="preserve"/>
+  </si>
+  <si>
     <t xml:space="preserve"> </t>
   </si>
   <si>
     <t>1.</t>
   </si>
   <si>
+    <t/>
+  </si>
+  <si>
     <t xml:space="preserve">Houseman </t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
     <t>3</t>
   </si>
   <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>Overnight</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
     <t/>
   </si>
   <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>Overnight</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
     <t>6</t>
   </si>
   <si>
+    <t xml:space="preserve"/>
+  </si>
+  <si>
     <t>Room per HM</t>
   </si>
   <si>
@@ -167,21 +209,27 @@
     <t>4th</t>
   </si>
   <si>
+    <t/>
+  </si>
+  <si>
+    <t>15th</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Total rooms per Lady</t>
+  </si>
+  <si>
+    <t>5th</t>
+  </si>
+  <si>
+    <t>16th</t>
+  </si>
+  <si>
     <t xml:space="preserve"/>
   </si>
   <si>
-    <t>15th</t>
-  </si>
-  <si>
-    <t>Total rooms per Lady</t>
-  </si>
-  <si>
-    <t>5th</t>
-  </si>
-  <si>
-    <t>16th</t>
-  </si>
-  <si>
     <t>6th</t>
   </si>
   <si>
@@ -194,6 +242,9 @@
     <t>7th</t>
   </si>
   <si>
+    <t/>
+  </si>
+  <si>
     <t>18th</t>
   </si>
   <si>
@@ -206,15 +257,27 @@
     <t>19th</t>
   </si>
   <si>
+    <t xml:space="preserve"/>
+  </si>
+  <si>
     <t>9th</t>
   </si>
   <si>
+    <t/>
+  </si>
+  <si>
     <t>20th</t>
   </si>
   <si>
+    <t xml:space="preserve"/>
+  </si>
+  <si>
     <t>10th</t>
   </si>
   <si>
+    <t/>
+  </si>
+  <si>
     <t>21st</t>
   </si>
   <si>
@@ -224,6 +287,9 @@
     <t>22nd</t>
   </si>
   <si>
+    <t xml:space="preserve"/>
+  </si>
+  <si>
     <t>12th</t>
   </si>
   <si>
@@ -254,9 +320,18 @@
     <t xml:space="preserve">Turndown </t>
   </si>
   <si>
+    <t/>
+  </si>
+  <si>
     <t>Rooms Found Vacant</t>
   </si>
   <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
     <t xml:space="preserve">  </t>
   </si>
   <si>
@@ -314,187 +389,103 @@
     <t>HR dia de/Day of</t>
   </si>
   <si>
+    <t>Monday</t>
+  </si>
+  <si>
     <t/>
   </si>
   <si>
     <t/>
   </si>
   <si>
+    <t>Time:</t>
+  </si>
+  <si>
+    <t>Lunch/Recess</t>
+  </si>
+  <si>
+    <t xml:space="preserve"/>
+  </si>
+  <si>
+    <t xml:space="preserve"/>
+  </si>
+  <si>
     <t/>
   </si>
   <si>
-    <t>Time:</t>
-  </si>
-  <si>
-    <t>Lunch/Recess</t>
-  </si>
-  <si>
     <t xml:space="preserve"/>
   </si>
   <si>
     <t xml:space="preserve"/>
   </si>
   <si>
-    <t>3:00pm</t>
+    <t>3.</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>2.</t>
   </si>
   <si>
     <t xml:space="preserve"/>
   </si>
   <si>
-    <t>3.</t>
+    <t xml:space="preserve"/>
+  </si>
+  <si>
+    <t>8.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PM Houseperson </t>
   </si>
   <si>
     <t/>
   </si>
   <si>
+    <t>HP Over night</t>
+  </si>
+  <si>
     <t/>
   </si>
   <si>
-    <t>2.</t>
-  </si>
-  <si>
     <t xml:space="preserve"/>
   </si>
   <si>
     <t xml:space="preserve"/>
   </si>
   <si>
-    <t>8.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PM Houseperson </t>
+    <t xml:space="preserve"/>
+  </si>
+  <si>
+    <t xml:space="preserve"/>
+  </si>
+  <si>
+    <t xml:space="preserve"/>
+  </si>
+  <si>
+    <t xml:space="preserve"/>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>HP Over night</t>
-  </si>
-  <si>
     <t/>
   </si>
   <si>
     <t xml:space="preserve"/>
   </si>
   <si>
+    <t>Room Found Vacant</t>
+  </si>
+  <si>
     <t xml:space="preserve"/>
-  </si>
-  <si>
-    <t xml:space="preserve"/>
-  </si>
-  <si>
-    <t xml:space="preserve"/>
-  </si>
-  <si>
-    <t xml:space="preserve"/>
-  </si>
-  <si>
-    <t xml:space="preserve"/>
-  </si>
-  <si>
-    <t xml:space="preserve"/>
-  </si>
-  <si>
-    <t xml:space="preserve"/>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t xml:space="preserve"/>
-  </si>
-  <si>
-    <t>Room Found Vacant</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t xml:space="preserve"/>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t xml:space="preserve"/>
-  </si>
-  <si>
-    <t xml:space="preserve"/>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t xml:space="preserve"/>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t xml:space="preserve"/>
-  </si>
-  <si>
-    <t xml:space="preserve"/>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t xml:space="preserve"/>
-  </si>
-  <si>
-    <t xml:space="preserve"/>
-  </si>
-  <si>
-    <t xml:space="preserve"/>
-  </si>
-  <si>
-    <t xml:space="preserve"/>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t/>
   </si>
 </sst>
 </file>
@@ -505,7 +496,7 @@
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="[$-409]m/d/yy\ h:mm\ AM/PM;@"/>
   </numFmts>
-  <fonts count="46" x14ac:knownFonts="1">
+  <fonts count="39">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -699,53 +690,7 @@
     </font>
     <font>
       <b/>
-      <sz val="14"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="10"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="16"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="20"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="14"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1469,7 +1414,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="332">
+  <cellXfs count="323">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2027,164 +1972,88 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="33" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="14" fontId="31" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="32" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="34" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="35" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="36" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="27" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="6" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="25" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="31" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="29" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="6" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="35" fillId="7" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="28" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="34" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="32" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="34" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="37" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="18" fontId="29" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="27" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="31" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="31" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="14" fontId="41" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="42" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="37" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="6" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="42" fillId="7" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="35" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="41" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="39" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="44" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="18" fontId="39" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="37" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="35" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="41" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="18" fontId="32" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="30" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="28" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="34" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="15" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -2209,9 +2078,86 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="38" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="16" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="16" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="15" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="18" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2238,102 +2184,78 @@
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="31" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="31" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="31" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="31" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="44" fillId="3" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="37" fillId="3" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="44" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="37" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="35" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="41" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="41" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="28" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="34" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="34" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection locked="0"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="16" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="16" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="15" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2574,10 +2496,6 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2927,62 +2845,62 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:ns4="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{65D85805-10C1-44A3-8067-B34748E36517}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65D85805-10C1-44A3-8067-B34748E36517}">
   <dimension ref="A1:W64"/>
-  <sheetFormatPr defaultColWidth="8.5546875" defaultRowHeight="21.6" customHeight="1" ns3:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="21.6" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="3" style="9" customWidth="1"/>
-    <col min="2" max="2" width="14.33203125" style="9" customWidth="1"/>
-    <col min="3" max="3" width="13.109375" style="9" customWidth="1"/>
-    <col min="4" max="4" width="12.6640625" style="9" customWidth="1"/>
-    <col min="5" max="5" width="15.109375" style="9" customWidth="1"/>
+    <col min="2" max="2" width="14.28515625" style="9" customWidth="1"/>
+    <col min="3" max="3" width="13.140625" style="9" customWidth="1"/>
+    <col min="4" max="4" width="12.7109375" style="9" customWidth="1"/>
+    <col min="5" max="5" width="15.140625" style="9" customWidth="1"/>
     <col min="6" max="6" width="13" style="9" customWidth="1"/>
-    <col min="7" max="7" width="12.6640625" style="9" customWidth="1"/>
-    <col min="8" max="8" width="2.109375" style="9" customWidth="1"/>
-    <col min="9" max="9" width="16.109375" style="9" customWidth="1"/>
-    <col min="10" max="10" width="16.44140625" style="9" customWidth="1"/>
-    <col min="11" max="11" width="61.6640625" style="9" customWidth="1"/>
+    <col min="7" max="7" width="12.7109375" style="9" customWidth="1"/>
+    <col min="8" max="8" width="2.140625" style="9" customWidth="1"/>
+    <col min="9" max="9" width="16.140625" style="9" customWidth="1"/>
+    <col min="10" max="10" width="16.42578125" style="9" customWidth="1"/>
+    <col min="11" max="11" width="61.7109375" style="9" customWidth="1"/>
     <col min="12" max="12" width="1" style="9" customWidth="1"/>
-    <col min="13" max="13" width="15.5546875" style="9" customWidth="1"/>
-    <col min="14" max="14" width="14.33203125" style="9" customWidth="1"/>
-    <col min="15" max="15" width="17.33203125" style="9" customWidth="1"/>
-    <col min="16" max="16384" width="8.5546875" style="9"/>
+    <col min="13" max="13" width="15.5703125" style="9" customWidth="1"/>
+    <col min="14" max="14" width="14.28515625" style="9" customWidth="1"/>
+    <col min="15" max="15" width="17.28515625" style="9" customWidth="1"/>
+    <col min="16" max="16384" width="8.5703125" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="21.6" customHeight="1" ns3:dyDescent="0.4">
-      <c r="K1" s="293"/>
-    </row>
-    <row r="2" spans="1:13" ht="21.6" customHeight="1" ns3:dyDescent="0.4">
+    <row r="1" spans="1:13" ht="21.6" customHeight="1">
+      <c r="K1" s="291"/>
+    </row>
+    <row r="2" spans="1:13" ht="21.6" customHeight="1">
       <c r="B2" s="10"/>
       <c r="C2" s="10"/>
       <c r="D2" s="10"/>
-      <c r="K2" s="293"/>
-    </row>
-    <row r="3" spans="1:13" ht="21.6" customHeight="1" ns3:dyDescent="0.4">
+      <c r="K2" s="291"/>
+    </row>
+    <row r="3" spans="1:13" ht="21.6" customHeight="1">
       <c r="B3" s="10"/>
       <c r="C3" s="10"/>
       <c r="D3" s="10"/>
       <c r="E3" s="10"/>
       <c r="F3" s="10"/>
       <c r="G3" s="10"/>
-      <c r="K3" s="293"/>
-    </row>
-    <row r="4" spans="1:13" ht="6.6" customHeight="1" ns3:dyDescent="0.4">
+      <c r="K3" s="291"/>
+    </row>
+    <row r="4" spans="1:13" ht="6.6" customHeight="1">
       <c r="B4" s="10"/>
       <c r="C4" s="10"/>
       <c r="D4" s="10"/>
       <c r="E4" s="10"/>
       <c r="F4" s="10"/>
       <c r="G4" s="10"/>
-      <c r="K4" s="293"/>
-    </row>
-    <row r="5" spans="1:13" ht="37.200000000000003" customHeight="1" ns3:dyDescent="0.4">
+      <c r="K4" s="291"/>
+    </row>
+    <row r="5" spans="1:13" ht="37.15" customHeight="1">
       <c r="A5" s="11"/>
-      <c r="B5" s="294" t="s">
+      <c r="B5" s="292" t="s">
         <v>0</v>
       </c>
-      <c r="C5" s="294"/>
-      <c r="D5" s="294"/>
+      <c r="C5" s="292"/>
+      <c r="D5" s="292"/>
       <c r="E5" s="173" t="s">
         <v>1</v>
       </c>
@@ -2992,50 +2910,64 @@
       <c r="G5" s="174" t="s">
         <v>3</v>
       </c>
-      <c r="K5" s="293"/>
-    </row>
-    <row r="6" spans="1:13" ht="21.6" customHeight="1" ns3:dyDescent="0.5">
+      <c r="K5" s="291"/>
+    </row>
+    <row r="6" spans="1:13" ht="21.6" customHeight="1">
       <c r="B6" s="191" t="s">
         <v>4</v>
       </c>
       <c r="C6" s="192">
         <f>(E6+F6)-G6</f>
+        <v>143</v>
       </c>
       <c r="D6" s="193"/>
-      <c r="E6" s="285"/>
-      <c r="F6" s="286"/>
-      <c r="G6" s="286"/>
+      <c r="E6" s="253">
+        <v>3</v>
+      </c>
+      <c r="F6" s="254">
+        <v>140</v>
+      </c>
+      <c r="G6" s="254"/>
       <c r="I6" s="200" t="s">
         <v>5</v>
       </c>
-      <c r="J6" s="159"/>
+      <c r="J6" s="159" t="s">
+        <v>6</v>
+      </c>
       <c r="K6" s="196" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" ht="21.6" customHeight="1" ns3:dyDescent="0.5">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="21.6" customHeight="1">
       <c r="B7" s="195" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C7" s="172">
         <f>(E7+F7)-G7</f>
+        <v>56</v>
       </c>
       <c r="D7" s="194"/>
-      <c r="E7" s="287"/>
-      <c r="F7" s="288"/>
-      <c r="G7" s="288"/>
+      <c r="E7" s="255">
+        <v>3</v>
+      </c>
+      <c r="F7" s="256">
+        <v>53</v>
+      </c>
+      <c r="G7" s="256"/>
       <c r="I7" s="201" t="s">
-        <v>8</v>
-      </c>
-      <c r="J7" s="190"/>
-      <c r="K7" s="290" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="8" spans="1:13" ht="21.6" customHeight="1" ns3:dyDescent="0.4">
+      <c r="J7" s="190" t="s">
+        <v>10</v>
+      </c>
+      <c r="K7" s="258" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="21.6" customHeight="1">
       <c r="A8" s="3"/>
       <c r="B8" s="156" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C8" s="10"/>
       <c r="D8" s="10"/>
@@ -3044,208 +2976,230 @@
       <c r="G8" s="10"/>
       <c r="H8" s="3"/>
       <c r="I8" s="155" t="s">
-        <v>11</v>
-      </c>
-      <c r="K8" s="292"/>
-    </row>
-    <row r="9" spans="1:13" ht="21.6" customHeight="1" ns3:dyDescent="0.4">
+        <v>13</v>
+      </c>
+      <c r="K8" s="260"/>
+    </row>
+    <row r="9" spans="1:13" ht="21.6" customHeight="1">
       <c r="B9" s="155" t="s">
-        <v>12</v>
-      </c>
-      <c r="C9" s="300"/>
-      <c r="D9" s="300"/>
-      <c r="E9" s="300"/>
+        <v>14</v>
+      </c>
+      <c r="C9" s="298" t="s">
+        <v>15</v>
+      </c>
+      <c r="D9" s="298"/>
+      <c r="E9" s="298"/>
       <c r="F9" s="27"/>
       <c r="G9" s="28"/>
       <c r="H9" s="3"/>
       <c r="I9" s="155" t="s">
-        <v>12</v>
-      </c>
-      <c r="J9" s="289"/>
-      <c r="K9" s="326"/>
+        <v>14</v>
+      </c>
+      <c r="J9" s="257" t="s">
+        <v>16</v>
+      </c>
+      <c r="K9" s="299"/>
       <c r="L9" s="3"/>
       <c r="M9" s="30"/>
     </row>
-    <row r="10" spans="1:13" ht="21.6" customHeight="1" ns3:dyDescent="0.4">
+    <row r="10" spans="1:13" ht="21.6" customHeight="1">
       <c r="F10" s="167"/>
-      <c r="K10" s="327"/>
-    </row>
-    <row r="11" spans="1:13" ht="21.6" customHeight="1" ns3:dyDescent="0.4">
-      <c r="B11" s="297" t="s">
-        <v>13</v>
-      </c>
-      <c r="C11" s="297"/>
+      <c r="K10" s="300"/>
+    </row>
+    <row r="11" spans="1:13" ht="21.6" customHeight="1">
+      <c r="B11" s="295" t="s">
+        <v>17</v>
+      </c>
+      <c r="C11" s="295"/>
       <c r="D11" s="180"/>
       <c r="E11" s="179" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F11" s="35"/>
       <c r="H11" s="28"/>
-      <c r="I11" s="298" t="s">
-        <v>15</v>
-      </c>
-      <c r="J11" s="298"/>
-      <c r="K11" s="291"/>
+      <c r="I11" s="296" t="s">
+        <v>19</v>
+      </c>
+      <c r="J11" s="296"/>
+      <c r="K11" s="259"/>
       <c r="L11" s="3"/>
       <c r="M11" s="35"/>
     </row>
-    <row r="12" spans="1:13" ht="21.6" customHeight="1" ns3:dyDescent="0.4">
+    <row r="12" spans="1:13" ht="21.6" customHeight="1">
       <c r="A12" s="36">
         <v>1</v>
       </c>
-      <c r="B12" s="330"/>
+      <c r="B12" s="265" t="s">
+        <v>20</v>
+      </c>
       <c r="E12" s="206"/>
       <c r="F12" s="205"/>
       <c r="H12" s="3">
         <v>1</v>
       </c>
-      <c r="I12" s="213"/>
+      <c r="I12" s="213" t="s">
+        <v>21</v>
+      </c>
       <c r="J12" s="160"/>
-      <c r="K12" s="291"/>
+      <c r="K12" s="259"/>
       <c r="L12" s="3"/>
       <c r="M12" s="35"/>
     </row>
-    <row r="13" spans="1:13" ht="21.6" customHeight="1" ns3:dyDescent="0.4">
+    <row r="13" spans="1:13" ht="21.6" customHeight="1">
       <c r="A13" s="36">
         <v>2</v>
       </c>
-      <c r="B13" s="330"/>
+      <c r="B13" s="265" t="s">
+        <v>22</v>
+      </c>
       <c r="E13" s="206"/>
       <c r="F13" s="205"/>
       <c r="H13" s="161"/>
       <c r="I13" s="162"/>
-      <c r="K13" s="291"/>
+      <c r="K13" s="259"/>
       <c r="M13" s="43"/>
     </row>
-    <row r="14" spans="1:13" ht="21.6" customHeight="1" ns3:dyDescent="0.4">
+    <row r="14" spans="1:13" ht="21.6" customHeight="1">
       <c r="A14" s="36">
         <v>3</v>
       </c>
-      <c r="B14" s="330"/>
+      <c r="B14" s="266"/>
       <c r="E14" s="206"/>
       <c r="F14" s="205"/>
       <c r="I14" s="175" t="s">
-        <v>16</v>
-      </c>
-      <c r="K14" s="291"/>
+        <v>23</v>
+      </c>
+      <c r="K14" s="259"/>
       <c r="M14" s="43"/>
     </row>
-    <row r="15" spans="1:13" ht="21.6" customHeight="1" ns3:dyDescent="0.4">
+    <row r="15" spans="1:13" ht="21.6" customHeight="1">
       <c r="A15" s="36">
         <v>4</v>
       </c>
-      <c r="B15" s="331"/>
+      <c r="B15" s="266"/>
       <c r="E15" s="206"/>
       <c r="F15" s="205"/>
       <c r="H15" s="166">
         <v>1</v>
       </c>
-      <c r="I15" s="213"/>
-      <c r="K15" s="291"/>
+      <c r="I15" s="213" t="s">
+        <v>24</v>
+      </c>
+      <c r="K15" s="259"/>
       <c r="M15" s="43"/>
     </row>
-    <row r="16" spans="1:13" ht="21.6" customHeight="1" ns3:dyDescent="0.4">
+    <row r="16" spans="1:13" ht="21.6" customHeight="1">
       <c r="A16" s="36">
         <v>5</v>
       </c>
-      <c r="B16" s="331"/>
+      <c r="B16" s="266"/>
       <c r="E16" s="206"/>
       <c r="F16" s="205"/>
       <c r="H16" s="166">
         <v>2</v>
       </c>
       <c r="I16" s="163"/>
-      <c r="K16" s="291"/>
+      <c r="K16" s="259"/>
       <c r="M16" s="43"/>
     </row>
-    <row r="17" spans="1:23" ht="21.6" customHeight="1" ns3:dyDescent="0.4">
+    <row r="17" spans="1:23" ht="21.6" customHeight="1">
       <c r="A17" s="28">
         <v>6</v>
       </c>
-      <c r="B17" s="331"/>
+      <c r="B17" s="266"/>
       <c r="C17" s="212"/>
       <c r="D17" s="212"/>
       <c r="E17" s="206"/>
       <c r="F17" s="205"/>
       <c r="I17" s="176" t="s">
-        <v>17</v>
-      </c>
-      <c r="K17" s="291"/>
+        <v>25</v>
+      </c>
+      <c r="K17" s="259"/>
       <c r="M17" s="43"/>
     </row>
-    <row r="18" spans="1:23" ht="21.6" customHeight="1" ns3:dyDescent="0.4">
+    <row r="18" spans="1:23" ht="21.6" customHeight="1">
       <c r="A18" s="48"/>
       <c r="E18" s="43"/>
       <c r="F18" s="43"/>
       <c r="H18" s="166">
         <v>1</v>
       </c>
-      <c r="I18" s="213"/>
-      <c r="K18" s="291"/>
+      <c r="I18" s="213" t="s">
+        <v>26</v>
+      </c>
+      <c r="K18" s="259"/>
       <c r="M18" s="43"/>
     </row>
-    <row r="19" spans="1:23" ht="21.6" customHeight="1" ns3:dyDescent="0.4">
+    <row r="19" spans="1:23" ht="21.6" customHeight="1">
       <c r="A19" s="28"/>
-      <c r="B19" s="295" t="s">
-        <v>18</v>
-      </c>
-      <c r="C19" s="295"/>
+      <c r="B19" s="293" t="s">
+        <v>27</v>
+      </c>
+      <c r="C19" s="293"/>
       <c r="D19" s="178"/>
       <c r="E19" s="179" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F19" s="51"/>
       <c r="H19" s="166">
         <v>2</v>
       </c>
-      <c r="I19" s="213"/>
+      <c r="I19" s="213" t="s">
+        <v>28</v>
+      </c>
       <c r="J19" s="3"/>
-      <c r="K19" s="291"/>
+      <c r="K19" s="259"/>
       <c r="L19" s="3"/>
       <c r="M19" s="35" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="20" spans="1:23" ht="21.6" customHeight="1" ns3:dyDescent="0.4">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="20" spans="1:23" ht="21.6" customHeight="1">
       <c r="A20" s="52" t="s">
-        <v>20</v>
-      </c>
-      <c r="B20" s="330"/>
+        <v>30</v>
+      </c>
+      <c r="B20" s="265" t="s">
+        <v>31</v>
+      </c>
       <c r="C20" s="157"/>
       <c r="E20" s="206"/>
       <c r="F20" s="205"/>
       <c r="I20" s="202" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="J20" s="170"/>
-      <c r="K20" s="291"/>
+      <c r="K20" s="259"/>
       <c r="L20" s="3"/>
       <c r="M20" s="35"/>
     </row>
-    <row r="21" spans="1:23" ht="21.6" customHeight="1" ns3:dyDescent="0.4">
+    <row r="21" spans="1:23" ht="21.6" customHeight="1">
       <c r="A21" s="56" t="s">
-        <v>22</v>
-      </c>
-      <c r="B21" s="330"/>
+        <v>33</v>
+      </c>
+      <c r="B21" s="265" t="s">
+        <v>34</v>
+      </c>
       <c r="E21" s="207"/>
       <c r="F21" s="205"/>
       <c r="G21" s="9" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="H21" s="166">
         <v>1</v>
       </c>
-      <c r="I21" s="284"/>
+      <c r="I21" s="252" t="s">
+        <v>35</v>
+      </c>
       <c r="J21" s="164"/>
-      <c r="K21" s="291"/>
+      <c r="K21" s="259"/>
       <c r="L21" s="3"/>
       <c r="M21" s="35"/>
     </row>
-    <row r="22" spans="1:23" ht="21.6" customHeight="1" ns3:dyDescent="0.4">
+    <row r="22" spans="1:23" ht="21.6" customHeight="1">
       <c r="A22" s="56" t="s">
-        <v>23</v>
-      </c>
-      <c r="B22" s="330"/>
+        <v>36</v>
+      </c>
+      <c r="B22" s="115"/>
       <c r="C22" s="157"/>
       <c r="E22" s="208"/>
       <c r="F22" s="205"/>
@@ -3254,31 +3208,31 @@
       </c>
       <c r="I22" s="203"/>
       <c r="J22" s="165"/>
-      <c r="K22" s="291"/>
+      <c r="K22" s="259"/>
       <c r="L22" s="3"/>
       <c r="M22" s="35"/>
     </row>
-    <row r="23" spans="1:23" ht="21.6" customHeight="1" ns3:dyDescent="0.4">
+    <row r="23" spans="1:23" ht="21.6" customHeight="1">
       <c r="A23" s="56" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="B23" s="115"/>
       <c r="E23" s="208"/>
       <c r="F23" s="205"/>
       <c r="I23" s="177" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="J23" s="165"/>
-      <c r="K23" s="291"/>
+      <c r="K23" s="259"/>
       <c r="L23" s="3"/>
       <c r="M23" s="35"/>
       <c r="W23" s="9" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="24" spans="1:23" ht="21.6" customHeight="1" ns3:dyDescent="0.4">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="24" spans="1:23" ht="21.6" customHeight="1">
       <c r="A24" s="56" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="B24" s="115"/>
       <c r="C24" s="157"/>
@@ -3288,13 +3242,15 @@
       <c r="H24" s="166">
         <v>1</v>
       </c>
-      <c r="I24" s="284"/>
+      <c r="I24" s="252" t="s">
+        <v>40</v>
+      </c>
       <c r="J24" s="165"/>
       <c r="K24" s="214"/>
     </row>
-    <row r="25" spans="1:23" ht="21.6" customHeight="1" ns3:dyDescent="0.4">
+    <row r="25" spans="1:23" ht="21.6" customHeight="1">
       <c r="A25" s="158" t="s">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="B25" s="115"/>
       <c r="C25" s="157"/>
@@ -3304,11 +3260,13 @@
       <c r="H25" s="169">
         <v>2</v>
       </c>
-      <c r="I25" s="284"/>
+      <c r="I25" s="252" t="s">
+        <v>42</v>
+      </c>
       <c r="J25" s="165"/>
       <c r="K25" s="214"/>
     </row>
-    <row r="26" spans="1:23" ht="21.6" customHeight="1" ns3:dyDescent="0.4">
+    <row r="26" spans="1:23" ht="21.6" customHeight="1">
       <c r="A26" s="60"/>
       <c r="B26" s="115"/>
       <c r="C26" s="197"/>
@@ -3322,41 +3280,41 @@
       <c r="J26" s="168"/>
       <c r="K26" s="214"/>
     </row>
-    <row r="27" spans="1:23" ht="21.6" customHeight="1" ns3:dyDescent="0.4">
+    <row r="27" spans="1:23" ht="21.6" customHeight="1">
       <c r="A27" s="60"/>
-      <c r="B27" s="299" t="s">
-        <v>29</v>
-      </c>
-      <c r="C27" s="299"/>
+      <c r="B27" s="297" t="s">
+        <v>43</v>
+      </c>
+      <c r="C27" s="297"/>
       <c r="D27" s="171">
         <f>C7/(COUNTA(B20:B25))</f>
-        <v>43.666666666666664</v>
+        <v>28</v>
       </c>
       <c r="F27" s="77"/>
       <c r="J27" s="168"/>
       <c r="K27" s="214"/>
     </row>
-    <row r="28" spans="1:23" ht="21.6" customHeight="1" ns3:dyDescent="0.4">
+    <row r="28" spans="1:23" ht="21.6" customHeight="1">
       <c r="A28" s="60"/>
-      <c r="B28" s="297" t="s">
-        <v>30</v>
-      </c>
-      <c r="C28" s="297"/>
+      <c r="B28" s="295" t="s">
+        <v>44</v>
+      </c>
+      <c r="C28" s="295"/>
       <c r="D28" s="171">
         <f>C7/(COUNTA(B12:B17))</f>
-        <v>43.666666666666664</v>
+        <v>28</v>
       </c>
       <c r="F28" s="77"/>
       <c r="J28" s="66"/>
       <c r="K28" s="214"/>
     </row>
-    <row r="29" spans="1:23" ht="21.6" customHeight="1" ns3:dyDescent="0.4">
+    <row r="29" spans="1:23" ht="21.6" customHeight="1">
       <c r="A29" s="60"/>
       <c r="F29" s="77"/>
       <c r="J29" s="168"/>
       <c r="K29" s="214"/>
     </row>
-    <row r="30" spans="1:23" ht="21.6" customHeight="1" ns3:dyDescent="0.4">
+    <row r="30" spans="1:23" ht="21.6" customHeight="1">
       <c r="A30" s="60"/>
       <c r="B30" s="11"/>
       <c r="C30" s="80"/>
@@ -3364,7 +3322,7 @@
       <c r="E30" s="3"/>
       <c r="F30" s="77"/>
     </row>
-    <row r="31" spans="1:23" ht="21.6" customHeight="1" ns3:dyDescent="0.4">
+    <row r="31" spans="1:23" ht="21.6" customHeight="1">
       <c r="A31" s="60"/>
       <c r="B31" s="11"/>
       <c r="C31" s="80"/>
@@ -3372,48 +3330,48 @@
       <c r="E31" s="3"/>
       <c r="F31" s="77"/>
     </row>
-    <row r="33" spans="2:23" ht="21.6" customHeight="1" thickBot="1" ns3:dyDescent="0.45"/>
-    <row r="34" spans="2:23" ht="21.6" customHeight="1" thickBot="1" ns3:dyDescent="0.45">
+    <row r="33" spans="2:23" ht="21.6" customHeight="1" thickBot="1"/>
+    <row r="34" spans="2:23" ht="21.6" customHeight="1" thickBot="1">
       <c r="C34" s="181" t="s">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="D34" s="182" t="s">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="E34" s="183" t="s">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="F34" s="181" t="s">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="G34" s="182" t="s">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="H34" s="183" t="s">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="I34" s="184"/>
     </row>
-    <row r="35" spans="2:23" ht="21.6" customHeight="1" thickBot="1" ns3:dyDescent="0.45">
+    <row r="35" spans="2:23" ht="21.6" customHeight="1" thickBot="1">
       <c r="C35" s="185" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="D35" s="7" t="str">
         <f>IF(E35="","",COUNTA($E35:E$35))</f>
         <v/>
       </c>
-      <c r="E35" s="324"/>
+      <c r="E35" s="261"/>
       <c r="F35" s="187" t="s">
-        <v>35</v>
-      </c>
-      <c r="G35" s="7">
+        <v>49</v>
+      </c>
+      <c r="G35" s="7" t="str">
         <f>IF(I35="","",(COUNTA($I$35:I35)+COUNTA($E$35:$E$45)))</f>
-        <v>8</v>
+        <v/>
       </c>
       <c r="H35" s="87"/>
-      <c r="I35" s="325"/>
+      <c r="I35" s="261"/>
       <c r="K35" s="127" t="s">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="P35" s="88"/>
       <c r="Q35" s="88"/>
@@ -3424,27 +3382,27 @@
       <c r="V35" s="89"/>
       <c r="W35" s="88"/>
     </row>
-    <row r="36" spans="2:23" ht="21.6" customHeight="1" thickBot="1" ns3:dyDescent="0.45">
+    <row r="36" spans="2:23" ht="21.6" customHeight="1" thickBot="1">
       <c r="C36" s="186" t="s">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="D36" s="7" t="str">
         <f>IF(E36="","",COUNTA($E$35:E36))</f>
         <v/>
       </c>
-      <c r="E36" s="324"/>
+      <c r="E36" s="261"/>
       <c r="F36" s="188" t="s">
-        <v>38</v>
-      </c>
-      <c r="G36" s="7">
+        <v>52</v>
+      </c>
+      <c r="G36" s="7" t="str">
         <f>IF(I36="","",(COUNTA($I$35:I36)+COUNTA($E$35:$E$45)))</f>
-        <v>9</v>
+        <v/>
       </c>
       <c r="H36" s="93"/>
-      <c r="I36" s="325"/>
+      <c r="I36" s="261"/>
       <c r="K36" s="94">
         <f>COUNTA(I35:I47,E35:E47)</f>
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="P36" s="88"/>
       <c r="R36" s="95"/>
@@ -3454,26 +3412,30 @@
       <c r="V36" s="96"/>
       <c r="W36" s="97"/>
     </row>
-    <row r="37" spans="2:23" ht="21.6" customHeight="1" thickBot="1" ns3:dyDescent="0.45">
+    <row r="37" spans="2:23" ht="21.6" customHeight="1" thickBot="1">
       <c r="C37" s="185" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="D37" s="7">
         <f>IF(E37="","",COUNTA($E$35:E37))</f>
         <v>1</v>
       </c>
-      <c r="E37" s="325"/>
+      <c r="E37" s="262" t="s">
+        <v>54</v>
+      </c>
       <c r="F37" s="187" t="s">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="G37" s="7">
         <f>IF(I37="","",(COUNTA($I$35:I37)+COUNTA($E$35:$E$45)))</f>
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H37" s="93"/>
-      <c r="I37" s="325"/>
+      <c r="I37" s="262" t="s">
+        <v>56</v>
+      </c>
       <c r="K37" s="130" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="P37" s="88"/>
       <c r="Q37" s="88"/>
@@ -3484,29 +3446,31 @@
       <c r="V37" s="96"/>
       <c r="W37" s="97"/>
     </row>
-    <row r="38" spans="2:23" ht="21.6" customHeight="1" thickBot="1" ns3:dyDescent="0.45">
+    <row r="38" spans="2:23" ht="21.6" customHeight="1" thickBot="1">
       <c r="C38" s="186" t="s">
-        <v>43</v>
-      </c>
-      <c r="D38" s="7">
+        <v>58</v>
+      </c>
+      <c r="D38" s="7" t="str">
         <f>IF(E38="","",COUNTA($E$35:E38))</f>
-        <v>2</v>
-      </c>
-      <c r="E38" s="325"/>
+        <v/>
+      </c>
+      <c r="E38" s="261"/>
       <c r="F38" s="188" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="G38" s="7">
         <f>IF(I38="","",(COUNTA($I$35:I38)+COUNTA($E$35:$E$45)))</f>
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="H38" s="93"/>
-      <c r="I38" s="325"/>
-      <c r="K38" s="296">
+      <c r="I38" s="262" t="s">
+        <v>60</v>
+      </c>
+      <c r="K38" s="294">
         <f>C6/K36</f>
-        <v>12.066666666666666</v>
-      </c>
-      <c r="L38" s="296"/>
+        <v>14.3</v>
+      </c>
+      <c r="L38" s="294"/>
       <c r="P38" s="88"/>
       <c r="Q38" s="88"/>
       <c r="R38" s="95"/>
@@ -3516,26 +3480,26 @@
       <c r="V38" s="96"/>
       <c r="W38" s="97"/>
     </row>
-    <row r="39" spans="2:23" ht="21.6" customHeight="1" thickBot="1" ns3:dyDescent="0.45">
+    <row r="39" spans="2:23" ht="21.6" customHeight="1" thickBot="1">
       <c r="C39" s="185" t="s">
-        <v>45</v>
+        <v>61</v>
       </c>
       <c r="D39" s="7" t="str">
         <f>IF(E39="","",COUNTA($E$35:E39))</f>
         <v/>
       </c>
-      <c r="E39" s="324"/>
+      <c r="E39" s="261"/>
       <c r="F39" s="187" t="s">
-        <v>46</v>
-      </c>
-      <c r="G39" s="7">
+        <v>62</v>
+      </c>
+      <c r="G39" s="7" t="str">
         <f>IF(I39="","",(COUNTA($I$35:I39)+COUNTA($E$35:$E$45)))</f>
-        <v>12</v>
+        <v/>
       </c>
       <c r="H39" s="93"/>
-      <c r="I39" s="325"/>
+      <c r="I39" s="261"/>
       <c r="K39" s="130" t="s">
-        <v>47</v>
+        <v>63</v>
       </c>
       <c r="P39" s="88"/>
       <c r="Q39" s="88"/>
@@ -3546,27 +3510,29 @@
       <c r="V39" s="96"/>
       <c r="W39" s="97"/>
     </row>
-    <row r="40" spans="2:23" ht="21.6" customHeight="1" ns3:dyDescent="0.4">
+    <row r="40" spans="2:23" ht="21.6" customHeight="1">
       <c r="C40" s="186" t="s">
-        <v>48</v>
+        <v>64</v>
       </c>
       <c r="D40" s="7">
         <f>IF(E40="","",COUNTA($E$35:E40))</f>
-        <v>3</v>
-      </c>
-      <c r="E40" s="325"/>
+        <v>2</v>
+      </c>
+      <c r="E40" s="262" t="s">
+        <v>65</v>
+      </c>
       <c r="F40" s="188" t="s">
-        <v>49</v>
-      </c>
-      <c r="G40" s="7">
+        <v>66</v>
+      </c>
+      <c r="G40" s="7" t="str">
         <f>IF(I40="","",(COUNTA($I$35:I40)+COUNTA($E$35:$E$45)))</f>
-        <v>13</v>
+        <v/>
       </c>
       <c r="H40" s="93"/>
-      <c r="I40" s="325"/>
+      <c r="I40" s="261"/>
       <c r="K40" s="125">
         <f>C7/K36</f>
-        <v>8.7333333333333325</v>
+        <v>5.6</v>
       </c>
       <c r="P40" s="88"/>
       <c r="Q40" s="88"/>
@@ -3577,24 +3543,28 @@
       <c r="V40" s="96"/>
       <c r="W40" s="97"/>
     </row>
-    <row r="41" spans="2:23" ht="21.6" customHeight="1" ns3:dyDescent="0.4">
+    <row r="41" spans="2:23" ht="21.6" customHeight="1">
       <c r="C41" s="185" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="D41" s="7">
         <f>IF(E41="","",COUNTA($E$35:E41))</f>
-        <v>4</v>
-      </c>
-      <c r="E41" s="325"/>
+        <v>3</v>
+      </c>
+      <c r="E41" s="262" t="s">
+        <v>68</v>
+      </c>
       <c r="F41" s="187" t="s">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="G41" s="7">
         <f>IF(I41="","",(COUNTA($I$35:I41)+COUNTA($E$35:$E$45)))</f>
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="H41" s="93"/>
-      <c r="I41" s="325"/>
+      <c r="I41" s="262" t="s">
+        <v>70</v>
+      </c>
       <c r="P41" s="88"/>
       <c r="R41" s="95"/>
       <c r="S41" s="96"/>
@@ -3603,24 +3573,28 @@
       <c r="V41" s="96"/>
       <c r="W41" s="97"/>
     </row>
-    <row r="42" spans="2:23" ht="21.6" customHeight="1" ns3:dyDescent="0.4">
+    <row r="42" spans="2:23" ht="21.6" customHeight="1">
       <c r="C42" s="186" t="s">
-        <v>53</v>
+        <v>71</v>
       </c>
       <c r="D42" s="7">
         <f>IF(E42="","",COUNTA($E$35:E42))</f>
-        <v>5</v>
-      </c>
-      <c r="E42" s="325"/>
+        <v>4</v>
+      </c>
+      <c r="E42" s="262" t="s">
+        <v>72</v>
+      </c>
       <c r="F42" s="188" t="s">
-        <v>54</v>
+        <v>73</v>
       </c>
       <c r="G42" s="7">
         <f>IF(I42="","",(COUNTA($I$35:I42)+COUNTA($E$35:$E$45)))</f>
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="H42" s="93"/>
-      <c r="I42" s="325"/>
+      <c r="I42" s="262" t="s">
+        <v>74</v>
+      </c>
       <c r="K42" s="204"/>
       <c r="P42" s="88"/>
       <c r="Q42" s="88"/>
@@ -3631,24 +3605,26 @@
       <c r="V42" s="96"/>
       <c r="W42" s="97"/>
     </row>
-    <row r="43" spans="2:23" ht="21.6" customHeight="1" ns3:dyDescent="0.4">
+    <row r="43" spans="2:23" ht="21.6" customHeight="1">
       <c r="C43" s="185" t="s">
-        <v>55</v>
-      </c>
-      <c r="D43" s="7" t="str">
+        <v>75</v>
+      </c>
+      <c r="D43" s="7">
         <f>IF(E43="","",COUNTA($E$35:E43))</f>
-        <v/>
-      </c>
-      <c r="E43" s="324"/>
+        <v>5</v>
+      </c>
+      <c r="E43" s="262" t="s">
+        <v>76</v>
+      </c>
       <c r="F43" s="187" t="s">
-        <v>56</v>
+        <v>77</v>
       </c>
       <c r="G43" s="7" t="str">
         <f>IF(I43="","",(COUNTA($I$35:I43)+COUNTA($E$35:$E$45)))</f>
         <v/>
       </c>
       <c r="H43" s="93"/>
-      <c r="I43" s="324"/>
+      <c r="I43" s="261"/>
       <c r="P43" s="88"/>
       <c r="Q43" s="88"/>
       <c r="R43" s="95"/>
@@ -3658,27 +3634,29 @@
       <c r="V43" s="96"/>
       <c r="W43" s="97"/>
     </row>
-    <row r="44" spans="2:23" ht="21.6" customHeight="1" ns3:dyDescent="0.4">
+    <row r="44" spans="2:23" ht="21.6" customHeight="1">
       <c r="B44" s="9" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="C44" s="186" t="s">
-        <v>57</v>
-      </c>
-      <c r="D44" s="7">
+        <v>78</v>
+      </c>
+      <c r="D44" s="7" t="str">
         <f>IF(E44="","",COUNTA($E$35:E44))</f>
-        <v>6</v>
-      </c>
-      <c r="E44" s="325"/>
+        <v/>
+      </c>
+      <c r="E44" s="261"/>
       <c r="F44" s="188" t="s">
-        <v>58</v>
-      </c>
-      <c r="G44" s="7" t="str">
+        <v>79</v>
+      </c>
+      <c r="G44" s="7">
         <f>IF(I44="","",(COUNTA($I$35:I44)+COUNTA($E$35:$E$45)))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="H44" s="93"/>
-      <c r="I44" s="324"/>
+      <c r="I44" s="262" t="s">
+        <v>80</v>
+      </c>
       <c r="P44" s="88"/>
       <c r="Q44" s="88"/>
       <c r="R44" s="95"/>
@@ -3688,18 +3666,18 @@
       <c r="V44" s="96"/>
       <c r="W44" s="97"/>
     </row>
-    <row r="45" spans="2:23" ht="21.6" customHeight="1" ns3:dyDescent="0.4">
+    <row r="45" spans="2:23" ht="21.6" customHeight="1">
       <c r="B45" s="98"/>
       <c r="C45" s="185" t="s">
-        <v>59</v>
-      </c>
-      <c r="D45" s="7">
+        <v>81</v>
+      </c>
+      <c r="D45" s="7" t="str">
         <f>IF(E45="","",COUNTA($E$35:E45))</f>
-        <v>7</v>
-      </c>
-      <c r="E45" s="325"/>
+        <v/>
+      </c>
+      <c r="E45" s="261"/>
       <c r="F45" s="189" t="s">
-        <v>60</v>
+        <v>82</v>
       </c>
       <c r="G45" s="7" t="str">
         <f>IF(I45="","",(COUNTA($I$35:I45)+COUNTA($E$35:$E$45)))</f>
@@ -3716,9 +3694,9 @@
       <c r="V45" s="96"/>
       <c r="W45" s="97"/>
     </row>
-    <row r="46" spans="2:23" ht="21.6" customHeight="1" ns3:dyDescent="0.4">
+    <row r="46" spans="2:23" ht="21.6" customHeight="1">
       <c r="C46" s="101" t="s">
-        <v>61</v>
+        <v>83</v>
       </c>
       <c r="D46" s="7" t="str">
         <f>IF(E46="","",COUNTA($E$36:E46))</f>
@@ -3726,7 +3704,7 @@
       </c>
       <c r="E46" s="211"/>
       <c r="F46" s="189" t="s">
-        <v>62</v>
+        <v>84</v>
       </c>
       <c r="G46" s="7" t="str">
         <f>IF(I46="","",(COUNTA($I$35:I46)+COUNTA($E$35:$E$45)))</f>
@@ -3743,7 +3721,7 @@
       <c r="V46" s="96"/>
       <c r="W46" s="97"/>
     </row>
-    <row r="47" spans="2:23" thickBot="1" ns3:dyDescent="0.45">
+    <row r="47" spans="2:23" thickBot="1">
       <c r="C47" s="104"/>
       <c r="D47" s="7" t="str">
         <f>IF(E47="","",COUNTA($E$36:E47))</f>
@@ -3751,7 +3729,7 @@
       </c>
       <c r="E47" s="118"/>
       <c r="F47" s="189" t="s">
-        <v>63</v>
+        <v>85</v>
       </c>
       <c r="G47" s="7" t="str">
         <f>IF(I47="","",(COUNTA($I$35:I47)+COUNTA($E$35:$E$45)))</f>
@@ -3760,7 +3738,7 @@
       <c r="H47" s="105"/>
       <c r="I47" s="211"/>
       <c r="J47" s="210" t="s">
-        <v>64</v>
+        <v>86</v>
       </c>
       <c r="K47" s="3"/>
       <c r="P47" s="88"/>
@@ -3772,44 +3750,50 @@
       <c r="V47" s="96"/>
       <c r="W47" s="96"/>
     </row>
-    <row r="48" spans="2:23" ht="21.6" customHeight="1" thickBot="1" ns3:dyDescent="0.45">
+    <row r="48" spans="2:23" ht="21.6" customHeight="1" thickBot="1">
       <c r="C48" s="107" t="s">
-        <v>65</v>
+        <v>87</v>
       </c>
       <c r="D48" s="107"/>
       <c r="F48" s="107" t="s">
-        <v>66</v>
+        <v>88</v>
       </c>
       <c r="G48" s="108"/>
       <c r="H48" s="108"/>
       <c r="I48" s="153"/>
       <c r="J48" s="209" t="s">
-        <v>67</v>
+        <v>89</v>
       </c>
       <c r="K48" s="198" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="49" spans="2:13" ht="21.6" customHeight="1" thickBot="1" ns3:dyDescent="0.45">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="49" spans="2:13" ht="21.6" customHeight="1" thickBot="1">
       <c r="C49" s="9">
         <v>1</v>
       </c>
-      <c r="E49" s="328"/>
+      <c r="E49" s="263" t="s">
+        <v>91</v>
+      </c>
       <c r="G49" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="J49" s="329"/>
+        <v>92</v>
+      </c>
+      <c r="J49" s="264">
+        <v>152</v>
+      </c>
       <c r="K49" s="9">
         <f>COUNTA(E49:E60)</f>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="50" spans="2:13" ht="21.6" customHeight="1" thickBot="1" ns3:dyDescent="0.45">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="50" spans="2:13" ht="21.6" customHeight="1" thickBot="1">
       <c r="C50" s="2">
         <v>2</v>
       </c>
       <c r="D50" s="2"/>
-      <c r="E50" s="328"/>
+      <c r="E50" s="263" t="s">
+        <v>35</v>
+      </c>
       <c r="F50" s="2">
         <v>1</v>
       </c>
@@ -3817,15 +3801,17 @@
       <c r="H50" s="75"/>
       <c r="I50" s="75"/>
       <c r="K50" s="199" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="51" spans="2:13" ht="21.6" customHeight="1" ns3:dyDescent="0.4">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="51" spans="2:13" ht="21.6" customHeight="1">
       <c r="C51" s="2">
         <v>3</v>
       </c>
       <c r="D51" s="2"/>
-      <c r="E51" s="328"/>
+      <c r="E51" s="263" t="s">
+        <v>93</v>
+      </c>
       <c r="F51" s="2">
         <v>2</v>
       </c>
@@ -3834,15 +3820,17 @@
       <c r="I51" s="75"/>
       <c r="K51" s="133">
         <f>J49/K49</f>
-        <v>44.333333333333336</v>
-      </c>
-    </row>
-    <row r="52" spans="2:13" ht="21.6" customHeight="1" ns3:dyDescent="0.4">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="52" spans="2:13" ht="21.6" customHeight="1">
       <c r="C52" s="2">
         <v>4</v>
       </c>
       <c r="D52" s="2"/>
-      <c r="E52" s="211"/>
+      <c r="E52" s="263" t="s">
+        <v>94</v>
+      </c>
       <c r="F52" s="2">
         <v>3</v>
       </c>
@@ -3851,7 +3839,7 @@
       <c r="I52" s="75"/>
       <c r="L52" s="122"/>
     </row>
-    <row r="53" spans="2:13" ht="21.6" customHeight="1" ns3:dyDescent="0.4">
+    <row r="53" spans="2:13" ht="21.6" customHeight="1">
       <c r="C53" s="2">
         <v>5</v>
       </c>
@@ -3864,7 +3852,7 @@
       <c r="H53" s="75"/>
       <c r="I53" s="75"/>
     </row>
-    <row r="54" spans="2:13" ht="21.6" customHeight="1" thickBot="1" ns3:dyDescent="0.45">
+    <row r="54" spans="2:13" ht="21.6" customHeight="1" thickBot="1">
       <c r="C54" s="2">
         <v>6</v>
       </c>
@@ -3877,7 +3865,7 @@
       <c r="H54" s="109"/>
       <c r="I54" s="109"/>
     </row>
-    <row r="55" spans="2:13" ht="21.6" customHeight="1" ns3:dyDescent="0.4">
+    <row r="55" spans="2:13" ht="21.6" customHeight="1">
       <c r="C55" s="2">
         <v>7</v>
       </c>
@@ -3888,10 +3876,10 @@
       <c r="H55" s="66"/>
       <c r="I55" s="66"/>
       <c r="M55" s="9" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="56" spans="2:13" ht="21.6" customHeight="1" ns3:dyDescent="0.4">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="56" spans="2:13" ht="21.6" customHeight="1">
       <c r="C56" s="2"/>
       <c r="D56" s="2"/>
       <c r="E56" s="138"/>
@@ -3900,7 +3888,7 @@
       <c r="H56" s="66"/>
       <c r="I56" s="66"/>
     </row>
-    <row r="57" spans="2:13" ht="21.6" customHeight="1" ns3:dyDescent="0.4">
+    <row r="57" spans="2:13" ht="21.6" customHeight="1">
       <c r="C57" s="1"/>
       <c r="D57" s="1"/>
       <c r="E57" s="66"/>
@@ -3909,25 +3897,25 @@
       <c r="H57" s="66"/>
       <c r="I57" s="66"/>
     </row>
-    <row r="58" spans="2:13" ht="21.6" customHeight="1" thickBot="1" ns3:dyDescent="0.45">
+    <row r="58" spans="2:13" ht="21.6" customHeight="1" thickBot="1">
       <c r="B58" s="4"/>
       <c r="C58" s="4" t="s">
-        <v>71</v>
+        <v>96</v>
       </c>
       <c r="D58" s="4"/>
       <c r="E58" s="5"/>
       <c r="F58" s="4" t="s">
-        <v>72</v>
+        <v>97</v>
       </c>
       <c r="G58" s="110"/>
       <c r="H58" s="110"/>
       <c r="I58" s="110"/>
       <c r="J58" s="4" t="s">
-        <v>73</v>
+        <v>98</v>
       </c>
       <c r="K58" s="111"/>
     </row>
-    <row r="59" spans="2:13" ht="21.6" customHeight="1" ns3:dyDescent="0.4">
+    <row r="59" spans="2:13" ht="21.6" customHeight="1">
       <c r="C59" s="1"/>
       <c r="D59" s="1"/>
       <c r="E59" s="3"/>
@@ -3936,7 +3924,7 @@
       <c r="H59" s="66"/>
       <c r="I59" s="66"/>
     </row>
-    <row r="60" spans="2:13" ht="21.6" customHeight="1" ns3:dyDescent="0.4">
+    <row r="60" spans="2:13" ht="21.6" customHeight="1">
       <c r="C60" s="66"/>
       <c r="D60" s="66"/>
       <c r="E60" s="3"/>
@@ -3945,7 +3933,7 @@
       <c r="H60" s="66"/>
       <c r="I60" s="66"/>
     </row>
-    <row r="61" spans="2:13" ht="21.6" customHeight="1" ns3:dyDescent="0.4">
+    <row r="61" spans="2:13" ht="21.6" customHeight="1">
       <c r="C61" s="66"/>
       <c r="D61" s="66"/>
       <c r="E61" s="66"/>
@@ -3954,23 +3942,23 @@
       <c r="H61" s="66"/>
       <c r="I61" s="66"/>
     </row>
-    <row r="62" spans="2:13" ht="21.6" customHeight="1" ns3:dyDescent="0.4">
+    <row r="62" spans="2:13" ht="21.6" customHeight="1">
       <c r="F62" s="66"/>
       <c r="G62" s="66"/>
       <c r="H62" s="66"/>
       <c r="I62" s="66"/>
       <c r="K62" s="9">
         <f>COUNTA(E49:E60)</f>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="63" spans="2:13" ht="21.6" customHeight="1" ns3:dyDescent="0.4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="2:13" ht="21.6" customHeight="1">
       <c r="F63" s="66"/>
       <c r="G63" s="66"/>
       <c r="H63" s="66"/>
       <c r="I63" s="66"/>
     </row>
-    <row r="64" spans="2:13" ht="21.6" customHeight="1" ns3:dyDescent="0.4">
+    <row r="64" spans="2:13" ht="21.6" customHeight="1">
       <c r="F64" s="66"/>
       <c r="G64" s="66"/>
       <c r="H64" s="66"/>
@@ -3994,126 +3982,194 @@
   <phoneticPr fontId="24" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup scale="75" orientation="landscape" ns4:id="rId1"/>
+  <pageSetup scale="75" orientation="landscape" r:id="rId1"/>
   <headerFooter alignWithMargins="0"/>
-  <drawing ns4:id="rId2"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:ns4="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A2:N13"/>
-  <sheetFormatPr defaultColWidth="8.5546875" defaultRowHeight="21.6" customHeight="1" ns3:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="21.6" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="3" style="215" customWidth="1"/>
-    <col min="2" max="2" width="24.5546875" style="215" customWidth="1"/>
-    <col min="3" max="3" width="21.5546875" style="215" customWidth="1"/>
-    <col min="4" max="4" width="14.6640625" style="215" customWidth="1"/>
-    <col min="5" max="5" width="16.33203125" style="215" customWidth="1"/>
-    <col min="6" max="6" width="13.5546875" style="215" customWidth="1"/>
-    <col min="7" max="7" width="9.5546875" style="215" customWidth="1"/>
+    <col min="2" max="2" width="24.5703125" style="215" customWidth="1"/>
+    <col min="3" max="3" width="21.5703125" style="215" customWidth="1"/>
+    <col min="4" max="4" width="14.7109375" style="215" customWidth="1"/>
+    <col min="5" max="5" width="16.28515625" style="215" customWidth="1"/>
+    <col min="6" max="6" width="13.5703125" style="215" customWidth="1"/>
+    <col min="7" max="7" width="9.5703125" style="215" customWidth="1"/>
     <col min="8" max="8" width="3" style="215" customWidth="1"/>
-    <col min="9" max="9" width="20.33203125" style="215" customWidth="1"/>
-    <col min="10" max="10" width="13.44140625" style="215" customWidth="1"/>
-    <col min="11" max="11" width="5.6640625" style="215" customWidth="1"/>
-    <col min="12" max="12" width="22.109375" style="215" customWidth="1"/>
-    <col min="13" max="13" width="3.5546875" style="215" customWidth="1"/>
-    <col min="14" max="14" width="15.6640625" style="215" customWidth="1"/>
-    <col min="15" max="15" width="8.6640625" style="215" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="1.6640625" style="215" customWidth="1"/>
-    <col min="17" max="17" width="8.6640625" style="215" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="8.5546875" style="215"/>
+    <col min="9" max="9" width="20.28515625" style="215" customWidth="1"/>
+    <col min="10" max="10" width="13.42578125" style="215" customWidth="1"/>
+    <col min="11" max="11" width="5.7109375" style="215" customWidth="1"/>
+    <col min="12" max="12" width="22.140625" style="215" customWidth="1"/>
+    <col min="13" max="13" width="3.5703125" style="215" customWidth="1"/>
+    <col min="14" max="14" width="15.7109375" style="215" customWidth="1"/>
+    <col min="15" max="15" width="8.7109375" style="215" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="1.7109375" style="215" customWidth="1"/>
+    <col min="17" max="17" width="8.7109375" style="215" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="8.5703125" style="215"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:14" ht="21.6" customHeight="1" ns3:dyDescent="0.5">
+    <row r="2" spans="1:14" ht="21.6" customHeight="1">
+      <c r="A2" s="9"/>
+      <c r="B2" s="9"/>
       <c r="C2" s="304" t="s">
-        <v>74</v>
+        <v>99</v>
       </c>
       <c r="D2" s="304"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9"/>
+      <c r="G2" s="9"/>
+      <c r="H2" s="9"/>
+      <c r="I2" s="9"/>
+      <c r="J2" s="9"/>
       <c r="K2" s="305"/>
       <c r="L2" s="305"/>
-    </row>
-    <row r="4" spans="1:14" ht="6.6" customHeight="1" ns3:dyDescent="0.4"/>
-    <row r="5" spans="1:14" ht="29.4" customHeight="1" ns3:dyDescent="0.4">
-      <c r="A5" s="216" t="s">
+      <c r="M2" s="9"/>
+      <c r="N2" s="9"/>
+    </row>
+    <row r="4" spans="1:14" ht="6.6" customHeight="1">
+      <c r="A4" s="9"/>
+      <c r="B4" s="9"/>
+      <c r="C4" s="9"/>
+      <c r="D4" s="9"/>
+      <c r="E4" s="9"/>
+      <c r="F4" s="9"/>
+      <c r="G4" s="9"/>
+      <c r="H4" s="9"/>
+      <c r="I4" s="9"/>
+      <c r="J4" s="9"/>
+      <c r="K4" s="9"/>
+      <c r="L4" s="9"/>
+      <c r="M4" s="9"/>
+      <c r="N4" s="9"/>
+    </row>
+    <row r="5" spans="1:14" ht="29.45" customHeight="1">
+      <c r="A5" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="D5" s="217" t="s">
-        <v>75</v>
-      </c>
-      <c r="E5" s="218" t="s">
-        <v>76</v>
-      </c>
-      <c r="F5" s="219" t="s">
+      <c r="B5" s="9"/>
+      <c r="C5" s="9"/>
+      <c r="D5" s="267" t="s">
+        <v>100</v>
+      </c>
+      <c r="E5" s="268" t="s">
+        <v>101</v>
+      </c>
+      <c r="F5" s="269" t="s">
         <v>2</v>
       </c>
-      <c r="G5" s="220" t="s">
-        <v>77</v>
-      </c>
-      <c r="J5" s="221"/>
-      <c r="K5" s="222"/>
-      <c r="L5" s="223"/>
-    </row>
-    <row r="6" spans="1:14" ht="21.6" customHeight="1" ns3:dyDescent="0.5">
-      <c r="B6" s="224" t="s">
-        <v>78</v>
-      </c>
-      <c r="C6" s="225">
+      <c r="G5" s="216" t="s">
+        <v>102</v>
+      </c>
+      <c r="H5" s="9"/>
+      <c r="I5" s="9"/>
+      <c r="J5" s="13"/>
+      <c r="K5" s="270"/>
+      <c r="L5" s="271"/>
+      <c r="M5" s="9"/>
+      <c r="N5" s="9"/>
+    </row>
+    <row r="6" spans="1:14" ht="21.6" customHeight="1">
+      <c r="A6" s="9"/>
+      <c r="B6" s="272" t="s">
+        <v>103</v>
+      </c>
+      <c r="C6" s="273">
         <f>D6+E6</f>
-      </c>
-      <c r="D6" s="226">
+        <v>265</v>
+      </c>
+      <c r="D6" s="274">
         <f>F6-G6</f>
-      </c>
-      <c r="E6" s="227"/>
-      <c r="F6" s="228"/>
-      <c r="G6" s="229"/>
-      <c r="J6" s="221"/>
-      <c r="K6" s="222"/>
-      <c r="L6" s="230"/>
-    </row>
-    <row r="7" spans="1:14" ht="21.6" customHeight="1" ns3:dyDescent="0.5">
-      <c r="B7" s="231" t="s">
-        <v>7</v>
-      </c>
-      <c r="C7" s="225">
+        <v>265</v>
+      </c>
+      <c r="E6" s="275"/>
+      <c r="F6" s="276">
+        <v>265</v>
+      </c>
+      <c r="G6" s="277"/>
+      <c r="H6" s="9"/>
+      <c r="I6" s="9"/>
+      <c r="J6" s="13"/>
+      <c r="K6" s="270"/>
+      <c r="L6" s="278"/>
+      <c r="M6" s="9"/>
+      <c r="N6" s="9"/>
+    </row>
+    <row r="7" spans="1:14" ht="21.6" customHeight="1">
+      <c r="A7" s="9"/>
+      <c r="B7" s="279" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="273">
         <f>D7+E7</f>
-      </c>
-      <c r="D7" s="226">
+        <v>83</v>
+      </c>
+      <c r="D7" s="274">
         <f>F7-G7</f>
-      </c>
-      <c r="E7" s="227"/>
-      <c r="F7" s="232"/>
-      <c r="G7" s="233"/>
-    </row>
-    <row r="8" spans="1:14" ht="21.6" customHeight="1" ns3:dyDescent="0.4">
-      <c r="F8" s="215" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" ht="21.6" customHeight="1" ns3:dyDescent="0.4">
-      <c r="A9" s="234"/>
-      <c r="B9" s="235"/>
-      <c r="C9" s="236"/>
+        <v>83</v>
+      </c>
+      <c r="E7" s="275"/>
+      <c r="F7" s="280">
+        <v>83</v>
+      </c>
+      <c r="G7" s="281"/>
+      <c r="H7" s="9"/>
+      <c r="I7" s="9"/>
+      <c r="J7" s="9"/>
+      <c r="K7" s="9"/>
+      <c r="L7" s="9"/>
+      <c r="M7" s="9"/>
+      <c r="N7" s="9"/>
+    </row>
+    <row r="8" spans="1:14" ht="21.6" customHeight="1">
+      <c r="A8" s="9"/>
+      <c r="B8" s="9"/>
+      <c r="C8" s="9"/>
+      <c r="D8" s="9"/>
+      <c r="E8" s="9"/>
+      <c r="F8" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="G8" s="9"/>
+      <c r="H8" s="9"/>
+      <c r="I8" s="9"/>
+      <c r="J8" s="9"/>
+      <c r="K8" s="9"/>
+      <c r="L8" s="9"/>
+      <c r="M8" s="9"/>
+      <c r="N8" s="9"/>
+    </row>
+    <row r="9" spans="1:14" ht="21.6" customHeight="1">
+      <c r="A9" s="3"/>
+      <c r="B9" s="282"/>
+      <c r="C9" s="283" t="s">
+        <v>105</v>
+      </c>
       <c r="D9" s="306" t="s">
-        <v>81</v>
+        <v>106</v>
       </c>
       <c r="E9" s="307"/>
-      <c r="F9" s="237"/>
-      <c r="H9" s="234"/>
-      <c r="I9" s="234"/>
-      <c r="J9" s="234"/>
-      <c r="K9" s="234"/>
-      <c r="L9" s="237"/>
-      <c r="M9" s="234"/>
-      <c r="N9" s="237"/>
-    </row>
-    <row r="10" spans="1:14" ht="21.6" customHeight="1" ns3:dyDescent="0.4">
-      <c r="A10" s="216"/>
-      <c r="B10" s="238" t="s">
-        <v>82</v>
-      </c>
-      <c r="C10" s="239">
+      <c r="F9" s="35"/>
+      <c r="G9" s="9"/>
+      <c r="H9" s="3"/>
+      <c r="I9" s="3"/>
+      <c r="J9" s="3"/>
+      <c r="K9" s="3"/>
+      <c r="L9" s="35"/>
+      <c r="M9" s="3"/>
+      <c r="N9" s="35"/>
+    </row>
+    <row r="10" spans="1:14" ht="21.6" customHeight="1">
+      <c r="A10" s="11"/>
+      <c r="B10" s="284" t="s">
+        <v>107</v>
+      </c>
+      <c r="C10" s="285">
         <v>4</v>
       </c>
       <c r="D10" s="308">
@@ -4121,21 +4177,22 @@
         <v>20.75</v>
       </c>
       <c r="E10" s="309"/>
-      <c r="F10" s="237"/>
-      <c r="H10" s="234"/>
-      <c r="I10" s="234"/>
-      <c r="J10" s="234"/>
-      <c r="K10" s="234"/>
-      <c r="L10" s="237"/>
-      <c r="M10" s="234"/>
-      <c r="N10" s="237"/>
-    </row>
-    <row r="11" spans="1:14" ht="21.6" customHeight="1" ns3:dyDescent="0.4">
-      <c r="A11" s="216"/>
-      <c r="B11" s="238" t="s">
-        <v>83</v>
-      </c>
-      <c r="C11" s="239">
+      <c r="F10" s="35"/>
+      <c r="G10" s="9"/>
+      <c r="H10" s="3"/>
+      <c r="I10" s="3"/>
+      <c r="J10" s="3"/>
+      <c r="K10" s="3"/>
+      <c r="L10" s="35"/>
+      <c r="M10" s="3"/>
+      <c r="N10" s="35"/>
+    </row>
+    <row r="11" spans="1:14" ht="21.6" customHeight="1">
+      <c r="A11" s="11"/>
+      <c r="B11" s="284" t="s">
+        <v>108</v>
+      </c>
+      <c r="C11" s="285">
         <v>4</v>
       </c>
       <c r="D11" s="310">
@@ -4143,40 +4200,61 @@
         <v>20.75</v>
       </c>
       <c r="E11" s="311"/>
-      <c r="F11" s="240"/>
-      <c r="H11" s="241"/>
-      <c r="I11" s="216"/>
-      <c r="L11" s="242"/>
-      <c r="N11" s="243"/>
-    </row>
-    <row r="12" spans="1:14" ht="22.95" customHeight="1" ns3:dyDescent="0.4">
-      <c r="A12" s="216"/>
-      <c r="B12" s="301"/>
+      <c r="F11" s="157"/>
+      <c r="G11" s="9"/>
+      <c r="H11" s="161"/>
+      <c r="I11" s="11"/>
+      <c r="J11" s="9"/>
+      <c r="K11" s="9"/>
+      <c r="L11" s="286"/>
+      <c r="M11" s="9"/>
+      <c r="N11" s="43"/>
+    </row>
+    <row r="12" spans="1:14" ht="22.9" customHeight="1">
+      <c r="A12" s="11"/>
+      <c r="B12" s="301" t="s">
+        <v>109</v>
+      </c>
       <c r="C12" s="303">
         <v>18</v>
       </c>
-      <c r="D12" s="244" t="s">
-        <v>85</v>
-      </c>
-      <c r="E12" s="245" t="s">
-        <v>86</v>
-      </c>
-      <c r="F12" s="240"/>
-      <c r="H12" s="241"/>
-      <c r="L12" s="246"/>
-      <c r="N12" s="243"/>
-    </row>
-    <row r="13" spans="1:14" ht="20.399999999999999" customHeight="1" ns3:dyDescent="0.4">
+      <c r="D12" s="155" t="s">
+        <v>110</v>
+      </c>
+      <c r="E12" s="287" t="s">
+        <v>111</v>
+      </c>
+      <c r="F12" s="157"/>
+      <c r="G12" s="9"/>
+      <c r="H12" s="161"/>
+      <c r="I12" s="9"/>
+      <c r="J12" s="9"/>
+      <c r="K12" s="9"/>
+      <c r="L12" s="288"/>
+      <c r="M12" s="9"/>
+      <c r="N12" s="43"/>
+    </row>
+    <row r="13" spans="1:14" ht="20.45" customHeight="1">
+      <c r="A13" s="9"/>
       <c r="B13" s="302"/>
       <c r="C13" s="303"/>
-      <c r="D13" s="247">
+      <c r="D13" s="289">
         <f>IF(C12="","",($C$6/C12))</f>
         <v>14.722222222222221</v>
       </c>
-      <c r="E13" s="248">
+      <c r="E13" s="290">
         <f>IF(C12="","",($C$7/C12))</f>
         <v>4.6111111111111107</v>
       </c>
+      <c r="F13" s="9"/>
+      <c r="G13" s="9"/>
+      <c r="H13" s="9"/>
+      <c r="I13" s="9"/>
+      <c r="J13" s="9"/>
+      <c r="K13" s="9"/>
+      <c r="L13" s="9"/>
+      <c r="M13" s="9"/>
+      <c r="N13" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -4190,121 +4268,131 @@
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" ns4:id="rId1"/>
+  <pageSetup orientation="landscape" r:id="rId1"/>
   <headerFooter alignWithMargins="0"/>
-  <drawing ns4:id="rId2"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:ns4="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{A345EC77-29E5-439A-85D5-D058CC333E3C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A345EC77-29E5-439A-85D5-D058CC333E3C}">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="A2:N61"/>
-  <sheetFormatPr defaultColWidth="8.5546875" defaultRowHeight="21.6" customHeight="1" ns3:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="21.6" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="3" style="249" customWidth="1"/>
-    <col min="2" max="2" width="24.5546875" style="249" customWidth="1"/>
-    <col min="3" max="3" width="21.5546875" style="249" customWidth="1"/>
-    <col min="4" max="4" width="14.6640625" style="249" customWidth="1"/>
-    <col min="5" max="5" width="16.33203125" style="249" customWidth="1"/>
-    <col min="6" max="6" width="13.5546875" style="249" customWidth="1"/>
-    <col min="7" max="7" width="9.5546875" style="249" customWidth="1"/>
-    <col min="8" max="8" width="3" style="249" customWidth="1"/>
-    <col min="9" max="9" width="20.33203125" style="249" customWidth="1"/>
-    <col min="10" max="10" width="13.44140625" style="249" customWidth="1"/>
-    <col min="11" max="11" width="5.6640625" style="249" customWidth="1"/>
-    <col min="12" max="12" width="22.109375" style="249" customWidth="1"/>
-    <col min="13" max="13" width="3.5546875" style="249" customWidth="1"/>
-    <col min="14" max="14" width="15.6640625" style="249" customWidth="1"/>
-    <col min="15" max="15" width="8.6640625" style="249" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="1.6640625" style="249" customWidth="1"/>
-    <col min="17" max="17" width="8.6640625" style="249" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="8.5546875" style="249"/>
+    <col min="1" max="1" width="3" style="217" customWidth="1"/>
+    <col min="2" max="2" width="24.5703125" style="217" customWidth="1"/>
+    <col min="3" max="3" width="21.5703125" style="217" customWidth="1"/>
+    <col min="4" max="4" width="14.7109375" style="217" customWidth="1"/>
+    <col min="5" max="5" width="16.28515625" style="217" customWidth="1"/>
+    <col min="6" max="6" width="13.5703125" style="217" customWidth="1"/>
+    <col min="7" max="7" width="9.5703125" style="217" customWidth="1"/>
+    <col min="8" max="8" width="3" style="217" customWidth="1"/>
+    <col min="9" max="9" width="20.28515625" style="217" customWidth="1"/>
+    <col min="10" max="10" width="13.42578125" style="217" customWidth="1"/>
+    <col min="11" max="11" width="5.7109375" style="217" customWidth="1"/>
+    <col min="12" max="12" width="22.140625" style="217" customWidth="1"/>
+    <col min="13" max="13" width="3.5703125" style="217" customWidth="1"/>
+    <col min="14" max="14" width="15.7109375" style="217" customWidth="1"/>
+    <col min="15" max="15" width="8.7109375" style="217" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="1.7109375" style="217" customWidth="1"/>
+    <col min="17" max="17" width="8.7109375" style="217" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="8.5703125" style="217"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:14" ht="21.6" customHeight="1" ns3:dyDescent="0.5">
+    <row r="2" spans="1:14" ht="21.6" customHeight="1">
       <c r="C2" s="317" t="s">
-        <v>87</v>
+        <v>112</v>
       </c>
       <c r="D2" s="317"/>
       <c r="K2" s="316"/>
       <c r="L2" s="316"/>
     </row>
-    <row r="4" spans="1:14" ht="6.6" customHeight="1" ns3:dyDescent="0.4"/>
-    <row r="5" spans="1:14" ht="21.6" customHeight="1" ns3:dyDescent="0.4">
-      <c r="A5" s="250" t="s">
+    <row r="4" spans="1:14" ht="6.6" customHeight="1"/>
+    <row r="5" spans="1:14" ht="21.6" customHeight="1">
+      <c r="A5" s="218" t="s">
         <v>0</v>
       </c>
-      <c r="D5" s="251" t="s">
-        <v>75</v>
-      </c>
-      <c r="E5" s="252" t="s">
-        <v>76</v>
-      </c>
-      <c r="F5" s="253" t="s">
+      <c r="D5" s="219" t="s">
+        <v>100</v>
+      </c>
+      <c r="E5" s="220" t="s">
+        <v>101</v>
+      </c>
+      <c r="F5" s="221" t="s">
         <v>2</v>
       </c>
-      <c r="G5" s="254" t="s">
-        <v>77</v>
-      </c>
-      <c r="J5" s="255"/>
-      <c r="K5" s="256"/>
-      <c r="L5" s="257"/>
-    </row>
-    <row r="6" spans="1:14" ht="21.6" customHeight="1" ns3:dyDescent="0.5">
-      <c r="B6" s="258" t="s">
-        <v>78</v>
-      </c>
-      <c r="C6" s="259">
+      <c r="G5" s="222" t="s">
+        <v>102</v>
+      </c>
+      <c r="J5" s="223"/>
+      <c r="K5" s="224"/>
+      <c r="L5" s="225"/>
+    </row>
+    <row r="6" spans="1:14" ht="21.6" customHeight="1">
+      <c r="B6" s="226" t="s">
+        <v>103</v>
+      </c>
+      <c r="C6" s="227">
         <f>D6+E6</f>
-      </c>
-      <c r="D6" s="260">
+        <v>243</v>
+      </c>
+      <c r="D6" s="228">
         <f>F6-G6</f>
-      </c>
-      <c r="E6" s="261"/>
-      <c r="F6" s="262"/>
-      <c r="G6" s="263"/>
-      <c r="J6" s="255"/>
-      <c r="K6" s="256"/>
-      <c r="L6" s="264"/>
-    </row>
-    <row r="7" spans="1:14" ht="21.6" customHeight="1" ns3:dyDescent="0.5">
-      <c r="B7" s="265" t="s">
-        <v>7</v>
-      </c>
-      <c r="C7" s="266">
+        <v>243</v>
+      </c>
+      <c r="E6" s="229"/>
+      <c r="F6" s="230">
+        <v>243</v>
+      </c>
+      <c r="G6" s="231"/>
+      <c r="J6" s="223"/>
+      <c r="K6" s="224"/>
+      <c r="L6" s="232"/>
+    </row>
+    <row r="7" spans="1:14" ht="21.6" customHeight="1">
+      <c r="B7" s="233" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="234">
         <f>D7+E7</f>
-      </c>
-      <c r="D7" s="260">
+        <v>151</v>
+      </c>
+      <c r="D7" s="228">
         <f>F7-G7</f>
-      </c>
-      <c r="E7" s="261"/>
-      <c r="F7" s="267"/>
-      <c r="G7" s="268"/>
-    </row>
-    <row r="9" spans="1:14" ht="21.6" customHeight="1" ns3:dyDescent="0.4">
-      <c r="A9" s="269"/>
-      <c r="B9" s="270"/>
-      <c r="C9" s="271"/>
+        <v>151</v>
+      </c>
+      <c r="E7" s="229"/>
+      <c r="F7" s="235">
+        <v>151</v>
+      </c>
+      <c r="G7" s="236"/>
+    </row>
+    <row r="9" spans="1:14" ht="21.6" customHeight="1">
+      <c r="A9" s="237"/>
+      <c r="B9" s="238"/>
+      <c r="C9" s="239" t="s">
+        <v>105</v>
+      </c>
       <c r="D9" s="318" t="s">
-        <v>81</v>
+        <v>106</v>
       </c>
       <c r="E9" s="319"/>
-      <c r="F9" s="272"/>
-      <c r="H9" s="269"/>
-      <c r="I9" s="269"/>
-      <c r="J9" s="269"/>
-      <c r="K9" s="269"/>
-      <c r="L9" s="272"/>
-      <c r="M9" s="269"/>
-      <c r="N9" s="272"/>
-    </row>
-    <row r="10" spans="1:14" ht="21.6" customHeight="1" ns3:dyDescent="0.4">
-      <c r="A10" s="250"/>
-      <c r="B10" s="273" t="s">
-        <v>82</v>
-      </c>
-      <c r="C10" s="274">
+      <c r="F9" s="240"/>
+      <c r="H9" s="237"/>
+      <c r="I9" s="237"/>
+      <c r="J9" s="237"/>
+      <c r="K9" s="237"/>
+      <c r="L9" s="240"/>
+      <c r="M9" s="237"/>
+      <c r="N9" s="240"/>
+    </row>
+    <row r="10" spans="1:14" ht="21.6" customHeight="1">
+      <c r="A10" s="218"/>
+      <c r="B10" s="241" t="s">
+        <v>107</v>
+      </c>
+      <c r="C10" s="242">
         <v>4</v>
       </c>
       <c r="D10" s="320">
@@ -4312,21 +4400,21 @@
         <v>37.75</v>
       </c>
       <c r="E10" s="321"/>
-      <c r="F10" s="272"/>
-      <c r="H10" s="269"/>
-      <c r="I10" s="269"/>
-      <c r="J10" s="269"/>
-      <c r="K10" s="269"/>
-      <c r="L10" s="272"/>
-      <c r="M10" s="269"/>
-      <c r="N10" s="272"/>
-    </row>
-    <row r="11" spans="1:14" ht="21.6" customHeight="1" ns3:dyDescent="0.4">
-      <c r="A11" s="250"/>
-      <c r="B11" s="273" t="s">
-        <v>83</v>
-      </c>
-      <c r="C11" s="274">
+      <c r="F10" s="240"/>
+      <c r="H10" s="237"/>
+      <c r="I10" s="237"/>
+      <c r="J10" s="237"/>
+      <c r="K10" s="237"/>
+      <c r="L10" s="240"/>
+      <c r="M10" s="237"/>
+      <c r="N10" s="240"/>
+    </row>
+    <row r="11" spans="1:14" ht="21.6" customHeight="1">
+      <c r="A11" s="218"/>
+      <c r="B11" s="241" t="s">
+        <v>108</v>
+      </c>
+      <c r="C11" s="242">
         <v>4</v>
       </c>
       <c r="D11" s="320">
@@ -4334,44 +4422,46 @@
         <v>37.75</v>
       </c>
       <c r="E11" s="321"/>
-      <c r="F11" s="275"/>
-      <c r="H11" s="276"/>
-      <c r="I11" s="250"/>
-      <c r="L11" s="277"/>
-      <c r="N11" s="278"/>
-    </row>
-    <row r="12" spans="1:14" ht="21.6" customHeight="1" ns3:dyDescent="0.4">
-      <c r="A12" s="250"/>
-      <c r="B12" s="312"/>
+      <c r="F11" s="243"/>
+      <c r="H11" s="244"/>
+      <c r="I11" s="218"/>
+      <c r="L11" s="245"/>
+      <c r="N11" s="246"/>
+    </row>
+    <row r="12" spans="1:14" ht="21.6" customHeight="1">
+      <c r="A12" s="218"/>
+      <c r="B12" s="312" t="s">
+        <v>109</v>
+      </c>
       <c r="C12" s="314">
         <v>16</v>
       </c>
-      <c r="D12" s="279" t="s">
-        <v>85</v>
-      </c>
-      <c r="E12" s="280" t="s">
-        <v>86</v>
-      </c>
-      <c r="F12" s="275"/>
-      <c r="H12" s="276"/>
-      <c r="L12" s="281"/>
-      <c r="N12" s="278"/>
-    </row>
-    <row r="13" spans="1:14" ht="21.6" customHeight="1" ns3:dyDescent="0.4">
+      <c r="D12" s="247" t="s">
+        <v>110</v>
+      </c>
+      <c r="E12" s="248" t="s">
+        <v>111</v>
+      </c>
+      <c r="F12" s="243"/>
+      <c r="H12" s="244"/>
+      <c r="L12" s="249"/>
+      <c r="N12" s="246"/>
+    </row>
+    <row r="13" spans="1:14" ht="21.6" customHeight="1">
       <c r="B13" s="313"/>
       <c r="C13" s="315"/>
-      <c r="D13" s="282">
+      <c r="D13" s="250">
         <f>IF(C12="","",($C$6/C12))</f>
         <v>15.1875</v>
       </c>
-      <c r="E13" s="282">
+      <c r="E13" s="250">
         <f>IF(C12="","",($C$7/C12))</f>
         <v>9.4375</v>
       </c>
     </row>
-    <row r="47" ht="21" ns3:dyDescent="0.4"/>
-    <row r="61" spans="5:5" ht="21.6" customHeight="1" ns3:dyDescent="0.4">
-      <c r="E61" s="283"/>
+    <row r="47" ht="21"/>
+    <row r="61" spans="5:5" ht="21.6" customHeight="1">
+      <c r="E61" s="251"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -4384,47 +4474,47 @@
     <mergeCell ref="D11:E11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="landscape" ns4:id="rId1"/>
-  <drawing ns4:id="rId2"/>
+  <pageSetup orientation="landscape" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:ns4="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A2:X64"/>
-  <sheetFormatPr defaultColWidth="8.5546875" defaultRowHeight="21.6" customHeight="1" ns3:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="21.6" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="3" style="9" customWidth="1"/>
-    <col min="2" max="2" width="24.5546875" style="9" customWidth="1"/>
-    <col min="3" max="3" width="21.5546875" style="9" customWidth="1"/>
+    <col min="2" max="2" width="24.5703125" style="9" customWidth="1"/>
+    <col min="3" max="3" width="21.5703125" style="9" customWidth="1"/>
     <col min="4" max="4" width="11" style="9" customWidth="1"/>
-    <col min="5" max="5" width="16.33203125" style="9" customWidth="1"/>
-    <col min="6" max="6" width="13.5546875" style="9" customWidth="1"/>
-    <col min="7" max="7" width="9.5546875" style="9" customWidth="1"/>
+    <col min="5" max="5" width="16.28515625" style="9" customWidth="1"/>
+    <col min="6" max="6" width="13.5703125" style="9" customWidth="1"/>
+    <col min="7" max="7" width="9.5703125" style="9" customWidth="1"/>
     <col min="8" max="8" width="3" style="9" customWidth="1"/>
-    <col min="9" max="9" width="20.44140625" style="9" customWidth="1"/>
-    <col min="10" max="10" width="13.44140625" style="9" customWidth="1"/>
-    <col min="11" max="11" width="5.6640625" style="9" customWidth="1"/>
-    <col min="12" max="12" width="24.88671875" style="9" customWidth="1"/>
-    <col min="13" max="13" width="3.5546875" style="9" customWidth="1"/>
-    <col min="14" max="14" width="15.5546875" style="9" customWidth="1"/>
-    <col min="15" max="15" width="8.5546875" style="9"/>
-    <col min="16" max="16" width="1.5546875" style="9" customWidth="1"/>
-    <col min="17" max="16384" width="8.5546875" style="9"/>
+    <col min="9" max="9" width="20.42578125" style="9" customWidth="1"/>
+    <col min="10" max="10" width="13.42578125" style="9" customWidth="1"/>
+    <col min="11" max="11" width="5.7109375" style="9" customWidth="1"/>
+    <col min="12" max="12" width="24.85546875" style="9" customWidth="1"/>
+    <col min="13" max="13" width="3.5703125" style="9" customWidth="1"/>
+    <col min="14" max="14" width="15.5703125" style="9" customWidth="1"/>
+    <col min="15" max="15" width="8.5703125" style="9"/>
+    <col min="16" max="16" width="1.5703125" style="9" customWidth="1"/>
+    <col min="17" max="16384" width="8.5703125" style="9"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:14" ht="21.6" customHeight="1" ns3:dyDescent="0.4">
+    <row r="2" spans="1:14" ht="21.6" customHeight="1">
       <c r="B2" s="10"/>
       <c r="C2" s="10"/>
       <c r="D2" s="10"/>
       <c r="E2" s="10"/>
       <c r="F2" s="10"/>
       <c r="G2" s="10"/>
-      <c r="K2" s="323"/>
-      <c r="L2" s="323"/>
-    </row>
-    <row r="3" spans="1:14" ht="21.6" customHeight="1" ns3:dyDescent="0.4">
+      <c r="K2" s="305"/>
+      <c r="L2" s="305"/>
+    </row>
+    <row r="3" spans="1:14" ht="21.6" customHeight="1">
       <c r="B3" s="10"/>
       <c r="C3" s="10"/>
       <c r="D3" s="10"/>
@@ -4434,7 +4524,7 @@
       <c r="K3" s="10"/>
       <c r="L3" s="10"/>
     </row>
-    <row r="4" spans="1:14" ht="6.6" customHeight="1" ns3:dyDescent="0.4">
+    <row r="4" spans="1:14" ht="6.6" customHeight="1">
       <c r="B4" s="10"/>
       <c r="C4" s="10"/>
       <c r="D4" s="10"/>
@@ -4444,77 +4534,91 @@
       <c r="K4" s="10"/>
       <c r="L4" s="10"/>
     </row>
-    <row r="5" spans="1:14" ht="37.200000000000003" customHeight="1" ns3:dyDescent="0.4">
+    <row r="5" spans="1:14" ht="37.15" customHeight="1">
       <c r="A5" s="11" t="s">
         <v>0</v>
       </c>
       <c r="B5" s="10"/>
       <c r="C5" s="10"/>
       <c r="D5" s="112" t="s">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>88</v>
+        <v>113</v>
       </c>
       <c r="F5" s="113" t="s">
         <v>2</v>
       </c>
       <c r="G5" s="114" t="s">
-        <v>77</v>
+        <v>102</v>
       </c>
       <c r="J5" s="13" t="s">
         <v>5</v>
       </c>
       <c r="K5" s="14" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="L5" s="15" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" ht="21.6" customHeight="1" ns3:dyDescent="0.5">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="21.6" customHeight="1">
       <c r="B6" s="16" t="s">
-        <v>78</v>
+        <v>103</v>
       </c>
       <c r="C6" s="17">
         <f>(E6+F6)-G6</f>
+        <v>151</v>
       </c>
       <c r="D6" s="18">
         <f>F6-G6</f>
-      </c>
-      <c r="E6" s="19"/>
-      <c r="F6" s="20"/>
+        <v>121</v>
+      </c>
+      <c r="E6" s="19">
+        <v>30</v>
+      </c>
+      <c r="F6" s="20">
+        <v>121</v>
+      </c>
       <c r="G6" s="21"/>
       <c r="I6" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="J6" s="13"/>
+        <v>29</v>
+      </c>
+      <c r="J6" s="13" t="s">
+        <v>9</v>
+      </c>
       <c r="K6" s="22" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="L6" s="23" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" ht="21.6" customHeight="1" ns3:dyDescent="0.5">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="21.6" customHeight="1">
       <c r="B7" s="24" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C7" s="17">
         <f>(E7+F7)-G7</f>
+        <v>89</v>
       </c>
       <c r="D7" s="18">
         <f>F7-G7</f>
-      </c>
-      <c r="E7" s="19"/>
-      <c r="F7" s="20"/>
+        <v>59</v>
+      </c>
+      <c r="E7" s="19">
+        <v>30</v>
+      </c>
+      <c r="F7" s="20">
+        <v>59</v>
+      </c>
       <c r="G7" s="21"/>
       <c r="K7" s="10"/>
       <c r="L7" s="10"/>
     </row>
-    <row r="8" spans="1:14" ht="21.6" customHeight="1" ns3:dyDescent="0.4">
+    <row r="8" spans="1:14" ht="21.6" customHeight="1">
       <c r="A8" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B8" s="10"/>
       <c r="C8" s="10"/>
@@ -4523,64 +4627,68 @@
       <c r="F8" s="10"/>
       <c r="G8" s="10"/>
       <c r="H8" s="3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I8" s="3"/>
       <c r="K8" s="10"/>
       <c r="L8" s="10"/>
     </row>
-    <row r="9" spans="1:14" ht="21.6" customHeight="1" ns3:dyDescent="0.4">
+    <row r="9" spans="1:14" ht="21.6" customHeight="1">
       <c r="A9" s="3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B9" s="3"/>
-      <c r="C9" s="25"/>
+      <c r="C9" s="25" t="s">
+        <v>116</v>
+      </c>
       <c r="D9" s="25"/>
       <c r="E9" s="26"/>
       <c r="F9" s="27"/>
       <c r="G9" s="28"/>
       <c r="H9" s="3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I9" s="3"/>
       <c r="J9" s="28"/>
       <c r="K9" s="25"/>
       <c r="L9" s="29" t="s">
-        <v>92</v>
+        <v>117</v>
       </c>
       <c r="M9" s="3"/>
       <c r="N9" s="30"/>
     </row>
-    <row r="11" spans="1:14" ht="21.6" customHeight="1" ns3:dyDescent="0.4">
+    <row r="11" spans="1:14" ht="21.6" customHeight="1">
       <c r="A11" s="28" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B11" s="31"/>
       <c r="C11" s="32" t="s">
-        <v>93</v>
+        <v>118</v>
       </c>
       <c r="D11" s="31"/>
       <c r="E11" s="33" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F11" s="34"/>
       <c r="H11" s="28" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="I11" s="28"/>
       <c r="J11" s="28"/>
       <c r="K11" s="3"/>
       <c r="L11" s="34" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="M11" s="3"/>
       <c r="N11" s="35"/>
     </row>
-    <row r="12" spans="1:14" ht="21.6" customHeight="1" ns3:dyDescent="0.4">
+    <row r="12" spans="1:14" ht="21.6" customHeight="1">
       <c r="A12" s="36">
         <v>1</v>
       </c>
-      <c r="B12" s="120"/>
+      <c r="B12" s="120" t="s">
+        <v>119</v>
+      </c>
       <c r="C12" s="37"/>
       <c r="D12" s="3"/>
       <c r="E12" s="38"/>
@@ -4588,54 +4696,60 @@
       <c r="H12" s="28">
         <v>1</v>
       </c>
-      <c r="I12" s="137"/>
+      <c r="I12" s="137" t="s">
+        <v>120</v>
+      </c>
       <c r="J12" s="28" t="s">
-        <v>96</v>
+        <v>121</v>
       </c>
       <c r="K12" s="3"/>
       <c r="L12" s="34"/>
       <c r="M12" s="3"/>
       <c r="N12" s="35"/>
     </row>
-    <row r="13" spans="1:14" ht="21.6" customHeight="1" ns3:dyDescent="0.4">
+    <row r="13" spans="1:14" ht="21.6" customHeight="1">
       <c r="A13" s="36">
         <v>2</v>
       </c>
-      <c r="B13" s="120"/>
+      <c r="B13" s="120" t="s">
+        <v>122</v>
+      </c>
       <c r="C13" s="37"/>
       <c r="D13" s="11"/>
       <c r="E13" s="38"/>
       <c r="F13" s="39"/>
       <c r="H13" s="40" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="I13" s="138"/>
       <c r="J13" s="41"/>
       <c r="L13" s="42"/>
       <c r="N13" s="43"/>
     </row>
-    <row r="14" spans="1:14" ht="21.6" customHeight="1" ns3:dyDescent="0.4">
+    <row r="14" spans="1:14" ht="21.6" customHeight="1">
       <c r="A14" s="36">
         <v>3</v>
       </c>
-      <c r="B14" s="139"/>
+      <c r="B14" s="139" t="s">
+        <v>123</v>
+      </c>
       <c r="C14" s="37"/>
       <c r="D14" s="11"/>
       <c r="E14" s="38"/>
       <c r="F14" s="39"/>
       <c r="H14" s="44" t="s">
-        <v>98</v>
+        <v>124</v>
       </c>
       <c r="I14" s="41" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J14" s="41"/>
       <c r="L14" s="45" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="N14" s="43"/>
     </row>
-    <row r="15" spans="1:14" ht="21.6" customHeight="1" ns3:dyDescent="0.4">
+    <row r="15" spans="1:14" ht="21.6" customHeight="1">
       <c r="A15" s="36">
         <v>4</v>
       </c>
@@ -4647,7 +4761,7 @@
       <c r="L15" s="43"/>
       <c r="N15" s="43"/>
     </row>
-    <row r="16" spans="1:14" ht="21.6" customHeight="1" ns3:dyDescent="0.4">
+    <row r="16" spans="1:14" ht="21.6" customHeight="1">
       <c r="A16" s="36">
         <v>5</v>
       </c>
@@ -4660,7 +4774,7 @@
       <c r="L16" s="43"/>
       <c r="N16" s="43"/>
     </row>
-    <row r="17" spans="1:24" ht="21.6" customHeight="1" ns3:dyDescent="0.4">
+    <row r="17" spans="1:24" ht="21.6" customHeight="1">
       <c r="A17" s="28">
         <v>6</v>
       </c>
@@ -4673,74 +4787,78 @@
       <c r="L17" s="43"/>
       <c r="N17" s="43"/>
     </row>
-    <row r="18" spans="1:24" ht="21.6" customHeight="1" ns3:dyDescent="0.4">
+    <row r="18" spans="1:24" ht="21.6" customHeight="1">
       <c r="A18" s="48"/>
       <c r="E18" s="43"/>
       <c r="F18" s="43"/>
       <c r="L18" s="43"/>
       <c r="N18" s="43"/>
     </row>
-    <row r="19" spans="1:24" ht="21.6" customHeight="1" ns3:dyDescent="0.4">
+    <row r="19" spans="1:24" ht="21.6" customHeight="1">
       <c r="A19" s="28" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="B19" s="49"/>
       <c r="C19" s="50" t="s">
-        <v>93</v>
+        <v>118</v>
       </c>
       <c r="D19" s="31"/>
       <c r="E19" s="33" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F19" s="51"/>
       <c r="H19" s="28" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="I19" s="28"/>
       <c r="J19" s="28"/>
       <c r="K19" s="3"/>
       <c r="L19" s="34" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="M19" s="3"/>
       <c r="N19" s="35" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="20" spans="1:24" ht="21.6" customHeight="1" ns3:dyDescent="0.4">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="20" spans="1:24" ht="21.6" customHeight="1">
       <c r="A20" s="52" t="s">
-        <v>20</v>
-      </c>
-      <c r="B20" s="140"/>
+        <v>30</v>
+      </c>
+      <c r="B20" s="140" t="s">
+        <v>125</v>
+      </c>
       <c r="C20" s="37"/>
       <c r="D20" s="3"/>
       <c r="E20" s="38"/>
       <c r="F20" s="39"/>
       <c r="H20" s="53" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="I20" s="120" t="s">
-        <v>99</v>
+        <v>126</v>
       </c>
       <c r="J20" s="54"/>
       <c r="L20" s="55"/>
       <c r="M20" s="3"/>
       <c r="N20" s="35"/>
     </row>
-    <row r="21" spans="1:24" ht="21.6" customHeight="1" ns3:dyDescent="0.4">
+    <row r="21" spans="1:24" ht="21.6" customHeight="1">
       <c r="A21" s="56" t="s">
-        <v>22</v>
-      </c>
-      <c r="B21" s="140"/>
+        <v>33</v>
+      </c>
+      <c r="B21" s="140" t="s">
+        <v>127</v>
+      </c>
       <c r="C21" s="57"/>
       <c r="D21" s="11"/>
       <c r="E21" s="38"/>
       <c r="F21" s="39"/>
       <c r="G21" s="9" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="H21" s="58" t="s">
-        <v>101</v>
+        <v>128</v>
       </c>
       <c r="I21" s="134"/>
       <c r="J21" s="54"/>
@@ -4748,29 +4866,31 @@
       <c r="M21" s="3"/>
       <c r="N21" s="35"/>
     </row>
-    <row r="22" spans="1:24" ht="21.6" customHeight="1" ns3:dyDescent="0.4">
+    <row r="22" spans="1:24" ht="21.6" customHeight="1">
       <c r="A22" s="56" t="s">
-        <v>23</v>
-      </c>
-      <c r="B22" s="154"/>
+        <v>36</v>
+      </c>
+      <c r="B22" s="154" t="s">
+        <v>129</v>
+      </c>
       <c r="C22" s="57"/>
       <c r="D22" s="47"/>
       <c r="E22" s="38"/>
       <c r="F22" s="39"/>
       <c r="H22" s="322" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="I22" s="322"/>
       <c r="J22" s="61" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="L22" s="62"/>
       <c r="M22" s="3"/>
       <c r="N22" s="35"/>
     </row>
-    <row r="23" spans="1:24" ht="21.6" customHeight="1" ns3:dyDescent="0.4">
+    <row r="23" spans="1:24" ht="21.6" customHeight="1">
       <c r="A23" s="56" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="B23" s="143"/>
       <c r="C23" s="57"/>
@@ -4779,19 +4899,19 @@
       <c r="F23" s="39"/>
       <c r="H23" s="60"/>
       <c r="I23" s="120" t="s">
-        <v>103</v>
+        <v>130</v>
       </c>
       <c r="J23" s="61"/>
       <c r="L23" s="63"/>
       <c r="M23" s="3"/>
       <c r="N23" s="35"/>
       <c r="X23" s="9" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="24" spans="1:24" ht="21.6" customHeight="1" ns3:dyDescent="0.4">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="24" spans="1:24" ht="21.6" customHeight="1">
       <c r="A24" s="56" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="B24" s="144"/>
       <c r="C24" s="57"/>
@@ -4799,29 +4919,29 @@
       <c r="E24" s="38"/>
       <c r="F24" s="39"/>
       <c r="H24" s="58" t="s">
-        <v>104</v>
+        <v>131</v>
       </c>
       <c r="I24" s="64"/>
       <c r="J24" s="61"/>
       <c r="L24" s="65"/>
     </row>
-    <row r="25" spans="1:24" ht="21.6" customHeight="1" ns3:dyDescent="0.4">
+    <row r="25" spans="1:24" ht="21.6" customHeight="1">
       <c r="A25" s="56" t="s">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="B25" s="116"/>
       <c r="C25" s="57"/>
       <c r="D25" s="47"/>
       <c r="F25" s="39"/>
       <c r="H25" s="3" t="s">
-        <v>105</v>
+        <v>132</v>
       </c>
       <c r="I25" s="66"/>
       <c r="J25" s="66"/>
       <c r="K25" s="66"/>
       <c r="L25" s="67"/>
     </row>
-    <row r="26" spans="1:24" ht="21.6" customHeight="1" ns3:dyDescent="0.4">
+    <row r="26" spans="1:24" ht="21.6" customHeight="1">
       <c r="A26" s="58"/>
       <c r="B26" s="116"/>
       <c r="C26" s="57"/>
@@ -4831,12 +4951,14 @@
       <c r="H26" s="1">
         <v>1</v>
       </c>
-      <c r="I26" s="120"/>
+      <c r="I26" s="120" t="s">
+        <v>133</v>
+      </c>
       <c r="J26" s="69"/>
       <c r="K26" s="70"/>
       <c r="L26" s="43"/>
     </row>
-    <row r="27" spans="1:24" ht="21.6" customHeight="1" ns3:dyDescent="0.4">
+    <row r="27" spans="1:24" ht="21.6" customHeight="1">
       <c r="A27" s="58"/>
       <c r="B27" s="71"/>
       <c r="C27" s="57"/>
@@ -4850,7 +4972,7 @@
       <c r="J27" s="74"/>
       <c r="K27" s="75"/>
     </row>
-    <row r="28" spans="1:24" ht="21.6" customHeight="1" ns3:dyDescent="0.4">
+    <row r="28" spans="1:24" ht="21.6" customHeight="1">
       <c r="A28" s="60"/>
       <c r="B28" s="11"/>
       <c r="C28" s="3"/>
@@ -4858,16 +4980,16 @@
       <c r="E28" s="76"/>
       <c r="F28" s="77"/>
       <c r="H28" s="2" t="s">
-        <v>107</v>
+        <v>134</v>
       </c>
       <c r="I28" s="75"/>
       <c r="J28" s="75"/>
       <c r="K28" s="75"/>
     </row>
-    <row r="29" spans="1:24" ht="21.6" customHeight="1" ns3:dyDescent="0.4">
+    <row r="29" spans="1:24" ht="21.6" customHeight="1">
       <c r="A29" s="60"/>
       <c r="B29" s="11" t="s">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="C29" s="78">
         <f>C7/(COUNTA(B20:B25))</f>
@@ -4880,12 +5002,12 @@
         <v>1</v>
       </c>
       <c r="I29" s="120" t="s">
-        <v>108</v>
+        <v>135</v>
       </c>
       <c r="J29" s="74"/>
       <c r="K29" s="75"/>
     </row>
-    <row r="30" spans="1:24" ht="21.6" customHeight="1" ns3:dyDescent="0.4">
+    <row r="30" spans="1:24" ht="21.6" customHeight="1">
       <c r="A30" s="60"/>
       <c r="B30" s="79"/>
       <c r="C30" s="3"/>
@@ -4896,10 +5018,10 @@
         <v>2</v>
       </c>
     </row>
-    <row r="31" spans="1:24" ht="21.6" customHeight="1" ns3:dyDescent="0.4">
+    <row r="31" spans="1:24" ht="21.6" customHeight="1">
       <c r="A31" s="60"/>
       <c r="B31" s="3" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="C31" s="78">
         <f>C7/(COUNTA(B12:B17))</f>
@@ -4909,7 +5031,7 @@
       <c r="E31" s="76"/>
       <c r="F31" s="77"/>
     </row>
-    <row r="32" spans="1:24" ht="21.6" customHeight="1" ns3:dyDescent="0.4">
+    <row r="32" spans="1:24" ht="21.6" customHeight="1">
       <c r="A32" s="60"/>
       <c r="B32" s="11"/>
       <c r="C32" s="80"/>
@@ -4917,52 +5039,56 @@
       <c r="E32" s="3"/>
       <c r="F32" s="77"/>
     </row>
-    <row r="33" spans="2:24" ht="21.6" customHeight="1" thickBot="1" ns3:dyDescent="0.45">
+    <row r="33" spans="2:24" ht="21.6" customHeight="1" thickBot="1">
       <c r="B33" s="9" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="34" spans="2:24" ht="21.6" customHeight="1" thickBot="1" ns3:dyDescent="0.45">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="34" spans="2:24" ht="21.6" customHeight="1" thickBot="1">
       <c r="C34" s="81" t="s">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="D34" s="82" t="s">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="E34" s="146" t="s">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="F34" s="81" t="s">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="G34" s="83" t="s">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="H34" s="84" t="s">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="I34" s="119"/>
     </row>
-    <row r="35" spans="2:24" ht="21.6" customHeight="1" thickBot="1" ns3:dyDescent="0.45">
+    <row r="35" spans="2:24" ht="21.6" customHeight="1" thickBot="1">
       <c r="C35" s="85" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="D35" s="7">
         <f>IF(E35="","",COUNTA($E$35:E35))</f>
         <v>1</v>
       </c>
-      <c r="E35" s="136"/>
+      <c r="E35" s="136" t="s">
+        <v>68</v>
+      </c>
       <c r="F35" s="86" t="s">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="G35" s="7">
         <f>IF(I35="","",(COUNTA($I$35:I35)+COUNTA($E$35:$E$45)))</f>
         <v>7</v>
       </c>
       <c r="H35" s="87"/>
-      <c r="I35" s="8"/>
+      <c r="I35" s="8" t="s">
+        <v>74</v>
+      </c>
       <c r="L35" s="127" t="s">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="Q35" s="88"/>
       <c r="R35" s="88"/>
@@ -4973,10 +5099,10 @@
       <c r="W35" s="89"/>
       <c r="X35" s="88"/>
     </row>
-    <row r="36" spans="2:24" ht="21.6" customHeight="1" thickBot="1" ns3:dyDescent="0.45">
+    <row r="36" spans="2:24" ht="21.6" customHeight="1" thickBot="1">
       <c r="B36" s="90"/>
       <c r="C36" s="91" t="s">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="D36" s="7" t="str">
         <f>IF(E36="","",COUNTA($E$35:E36))</f>
@@ -4984,7 +5110,7 @@
       </c>
       <c r="E36" s="148"/>
       <c r="F36" s="92" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="G36" s="7" t="str">
         <f>IF(I36="","",(COUNTA($I$35:I36)+COUNTA($E$35:$E$45)))</f>
@@ -5004,10 +5130,10 @@
       <c r="W36" s="96"/>
       <c r="X36" s="97"/>
     </row>
-    <row r="37" spans="2:24" ht="21.6" customHeight="1" thickBot="1" ns3:dyDescent="0.45">
+    <row r="37" spans="2:24" ht="21.6" customHeight="1" thickBot="1">
       <c r="B37" s="90"/>
       <c r="C37" s="85" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="D37" s="7" t="str">
         <f>IF(E37="","",COUNTA($E$35:E37))</f>
@@ -5015,16 +5141,18 @@
       </c>
       <c r="E37" s="149"/>
       <c r="F37" s="86" t="s">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="G37" s="7">
         <f>IF(I37="","",(COUNTA($I$35:I37)+COUNTA($E$35:$E$45)))</f>
         <v>8</v>
       </c>
       <c r="H37" s="93"/>
-      <c r="I37" s="121"/>
+      <c r="I37" s="121" t="s">
+        <v>136</v>
+      </c>
       <c r="L37" s="130" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="Q37" s="88"/>
       <c r="R37" s="88"/>
@@ -5035,10 +5163,10 @@
       <c r="W37" s="96"/>
       <c r="X37" s="97"/>
     </row>
-    <row r="38" spans="2:24" ht="21.6" customHeight="1" thickBot="1" ns3:dyDescent="0.45">
+    <row r="38" spans="2:24" ht="21.6" customHeight="1" thickBot="1">
       <c r="B38" s="98"/>
       <c r="C38" s="91" t="s">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="D38" s="7" t="str">
         <f>IF(E38="","",COUNTA($E$35:E38))</f>
@@ -5046,20 +5174,22 @@
       </c>
       <c r="E38" s="149"/>
       <c r="F38" s="92" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="G38" s="7">
         <f>IF(I38="","",(COUNTA($I$35:I38)+COUNTA($E$35:$E$45)))</f>
         <v>9</v>
       </c>
       <c r="H38" s="93"/>
-      <c r="I38" s="8"/>
+      <c r="I38" s="8" t="s">
+        <v>60</v>
+      </c>
       <c r="K38" s="124"/>
-      <c r="L38" s="296">
+      <c r="L38" s="294">
         <f>C6/L36</f>
         <v>15.1</v>
       </c>
-      <c r="M38" s="296"/>
+      <c r="M38" s="294"/>
       <c r="Q38" s="88"/>
       <c r="R38" s="88"/>
       <c r="S38" s="95"/>
@@ -5069,9 +5199,9 @@
       <c r="W38" s="96"/>
       <c r="X38" s="97"/>
     </row>
-    <row r="39" spans="2:24" ht="21.6" customHeight="1" thickBot="1" ns3:dyDescent="0.45">
+    <row r="39" spans="2:24" ht="21.6" customHeight="1" thickBot="1">
       <c r="C39" s="85" t="s">
-        <v>45</v>
+        <v>61</v>
       </c>
       <c r="D39" s="7" t="str">
         <f>IF(E39="","",COUNTA($E$35:E39))</f>
@@ -5079,17 +5209,19 @@
       </c>
       <c r="E39" s="149"/>
       <c r="F39" s="86" t="s">
-        <v>46</v>
+        <v>62</v>
       </c>
       <c r="G39" s="7">
         <f>IF(I39="","",(COUNTA($I$35:I39)+COUNTA($E$35:$E$45)))</f>
         <v>10</v>
       </c>
       <c r="H39" s="93"/>
-      <c r="I39" s="121"/>
+      <c r="I39" s="121" t="s">
+        <v>137</v>
+      </c>
       <c r="K39" s="122"/>
       <c r="L39" s="130" t="s">
-        <v>47</v>
+        <v>63</v>
       </c>
       <c r="Q39" s="88"/>
       <c r="R39" s="88"/>
@@ -5100,17 +5232,19 @@
       <c r="W39" s="96"/>
       <c r="X39" s="97"/>
     </row>
-    <row r="40" spans="2:24" ht="21.6" customHeight="1" ns3:dyDescent="0.4">
+    <row r="40" spans="2:24" ht="21.6" customHeight="1">
       <c r="C40" s="91" t="s">
-        <v>48</v>
+        <v>64</v>
       </c>
       <c r="D40" s="7">
         <f>IF(E40="","",COUNTA($E$35:E40))</f>
         <v>2</v>
       </c>
-      <c r="E40" s="8"/>
+      <c r="E40" s="8" t="s">
+        <v>138</v>
+      </c>
       <c r="F40" s="92" t="s">
-        <v>49</v>
+        <v>66</v>
       </c>
       <c r="G40" s="7" t="str">
         <f>IF(I40="","",(COUNTA($I$35:I40)+COUNTA($E$35:$E$45)))</f>
@@ -5131,17 +5265,19 @@
       <c r="W40" s="96"/>
       <c r="X40" s="97"/>
     </row>
-    <row r="41" spans="2:24" ht="21.6" customHeight="1" ns3:dyDescent="0.4">
+    <row r="41" spans="2:24" ht="21.6" customHeight="1">
       <c r="C41" s="85" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="D41" s="7">
         <f>IF(E41="","",COUNTA($E$35:E41))</f>
         <v>3</v>
       </c>
-      <c r="E41" s="8"/>
+      <c r="E41" s="8" t="s">
+        <v>139</v>
+      </c>
       <c r="F41" s="86" t="s">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="G41" s="7" t="str">
         <f>IF(I41="","",(COUNTA($I$35:I41)+COUNTA($E$35:$E$45)))</f>
@@ -5157,17 +5293,19 @@
       <c r="W41" s="96"/>
       <c r="X41" s="97"/>
     </row>
-    <row r="42" spans="2:24" ht="21.6" customHeight="1" ns3:dyDescent="0.4">
+    <row r="42" spans="2:24" ht="21.6" customHeight="1">
       <c r="C42" s="91" t="s">
-        <v>53</v>
+        <v>71</v>
       </c>
       <c r="D42" s="7">
         <f>IF(E42="","",COUNTA($E$35:E42))</f>
         <v>4</v>
       </c>
-      <c r="E42" s="8"/>
+      <c r="E42" s="8" t="s">
+        <v>140</v>
+      </c>
       <c r="F42" s="92" t="s">
-        <v>54</v>
+        <v>73</v>
       </c>
       <c r="G42" s="7" t="str">
         <f>IF(I42="","",(COUNTA($I$35:I42)+COUNTA($E$35:$E$45)))</f>
@@ -5184,17 +5322,19 @@
       <c r="W42" s="96"/>
       <c r="X42" s="97"/>
     </row>
-    <row r="43" spans="2:24" ht="21.6" customHeight="1" ns3:dyDescent="0.4">
+    <row r="43" spans="2:24" ht="21.6" customHeight="1">
       <c r="C43" s="85" t="s">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="D43" s="7">
         <f>IF(E43="","",COUNTA($E$35:E43))</f>
         <v>5</v>
       </c>
-      <c r="E43" s="8"/>
+      <c r="E43" s="8" t="s">
+        <v>141</v>
+      </c>
       <c r="F43" s="86" t="s">
-        <v>56</v>
+        <v>77</v>
       </c>
       <c r="G43" s="7" t="str">
         <f>IF(I43="","",(COUNTA($I$35:I43)+COUNTA($E$35:$E$45)))</f>
@@ -5211,12 +5351,12 @@
       <c r="W43" s="96"/>
       <c r="X43" s="97"/>
     </row>
-    <row r="44" spans="2:24" ht="21.6" customHeight="1" ns3:dyDescent="0.4">
+    <row r="44" spans="2:24" ht="21.6" customHeight="1">
       <c r="B44" s="9" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="C44" s="91" t="s">
-        <v>57</v>
+        <v>78</v>
       </c>
       <c r="D44" s="7" t="str">
         <f>IF(E44="","",COUNTA($E$35:E44))</f>
@@ -5224,7 +5364,7 @@
       </c>
       <c r="E44" s="150"/>
       <c r="F44" s="92" t="s">
-        <v>58</v>
+        <v>79</v>
       </c>
       <c r="G44" s="7" t="str">
         <f>IF(I44="","",(COUNTA($I$35:I44)+COUNTA($E$35:$E$45)))</f>
@@ -5241,18 +5381,20 @@
       <c r="W44" s="96"/>
       <c r="X44" s="97"/>
     </row>
-    <row r="45" spans="2:24" ht="21.6" customHeight="1" ns3:dyDescent="0.4">
+    <row r="45" spans="2:24" ht="21.6" customHeight="1">
       <c r="B45" s="98"/>
       <c r="C45" s="85" t="s">
-        <v>59</v>
+        <v>81</v>
       </c>
       <c r="D45" s="7">
         <f>IF(E45="","",COUNTA($E$35:E45))</f>
         <v>6</v>
       </c>
-      <c r="E45" s="8"/>
+      <c r="E45" s="8" t="s">
+        <v>142</v>
+      </c>
       <c r="F45" s="99" t="s">
-        <v>60</v>
+        <v>82</v>
       </c>
       <c r="G45" s="7" t="str">
         <f>IF(I45="","",(COUNTA($I$35:I45)+COUNTA($E$35:$E$45)))</f>
@@ -5269,14 +5411,14 @@
       <c r="W45" s="96"/>
       <c r="X45" s="97"/>
     </row>
-    <row r="46" spans="2:24" ht="21.6" customHeight="1" thickBot="1" ns3:dyDescent="0.45">
+    <row r="46" spans="2:24" ht="21.6" customHeight="1" thickBot="1">
       <c r="C46" s="101" t="s">
-        <v>61</v>
+        <v>83</v>
       </c>
       <c r="D46" s="102"/>
       <c r="E46" s="135"/>
       <c r="F46" s="99" t="s">
-        <v>62</v>
+        <v>84</v>
       </c>
       <c r="G46" s="7" t="str">
         <f>IF(I46="","",(COUNTA($I$35:I46)+COUNTA($E$35:$E$45)))</f>
@@ -5293,7 +5435,7 @@
       <c r="W46" s="96"/>
       <c r="X46" s="97"/>
     </row>
-    <row r="47" spans="2:24" thickBot="1" ns3:dyDescent="0.45">
+    <row r="47" spans="2:24" thickBot="1">
       <c r="C47" s="104"/>
       <c r="D47" s="105"/>
       <c r="E47" s="118"/>
@@ -5310,52 +5452,54 @@
       <c r="W47" s="96"/>
       <c r="X47" s="96"/>
     </row>
-    <row r="48" spans="2:24" ht="21.6" customHeight="1" thickBot="1" ns3:dyDescent="0.45">
+    <row r="48" spans="2:24" ht="21.6" customHeight="1" thickBot="1">
       <c r="C48" s="107" t="s">
-        <v>65</v>
+        <v>87</v>
       </c>
       <c r="D48" s="107"/>
       <c r="F48" s="107" t="s">
-        <v>66</v>
+        <v>88</v>
       </c>
       <c r="G48" s="108"/>
       <c r="H48" s="108"/>
       <c r="I48" s="152" t="s">
-        <v>118</v>
+        <v>143</v>
       </c>
       <c r="J48" s="126" t="s">
-        <v>67</v>
+        <v>89</v>
       </c>
       <c r="L48" s="128" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="49" spans="2:14" ht="21.6" customHeight="1" thickBot="1" ns3:dyDescent="0.45">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="49" spans="2:14" ht="21.6" customHeight="1" thickBot="1">
       <c r="C49" s="2">
         <v>1</v>
       </c>
       <c r="D49" s="145" t="s">
-        <v>119</v>
+        <v>144</v>
       </c>
       <c r="E49" s="6"/>
       <c r="F49" s="2"/>
       <c r="G49" s="28" t="s">
-        <v>120</v>
+        <v>145</v>
       </c>
       <c r="H49" s="70"/>
       <c r="I49" s="70"/>
-      <c r="J49" s="131"/>
+      <c r="J49" s="131">
+        <v>153</v>
+      </c>
       <c r="L49" s="132">
         <f>COUNTA(D49:D60)</f>
         <v>4</v>
       </c>
     </row>
-    <row r="50" spans="2:14" ht="21.6" customHeight="1" thickBot="1" ns3:dyDescent="0.45">
+    <row r="50" spans="2:14" ht="21.6" customHeight="1" thickBot="1">
       <c r="C50" s="2">
         <v>2</v>
       </c>
       <c r="D50" s="145" t="s">
-        <v>121</v>
+        <v>91</v>
       </c>
       <c r="E50" s="6"/>
       <c r="F50" s="2">
@@ -5365,15 +5509,15 @@
       <c r="H50" s="75"/>
       <c r="I50" s="75"/>
       <c r="L50" s="129" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="51" spans="2:14" ht="21.6" customHeight="1" thickBot="1" ns3:dyDescent="0.45">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="51" spans="2:14" ht="21.6" customHeight="1" thickBot="1">
       <c r="C51" s="2">
         <v>3</v>
       </c>
       <c r="D51" s="145" t="s">
-        <v>122</v>
+        <v>146</v>
       </c>
       <c r="E51" s="6"/>
       <c r="F51" s="2">
@@ -5387,12 +5531,12 @@
         <v>38.25</v>
       </c>
     </row>
-    <row r="52" spans="2:14" ht="21.6" customHeight="1" thickBot="1" ns3:dyDescent="0.45">
+    <row r="52" spans="2:14" ht="21.6" customHeight="1" thickBot="1">
       <c r="C52" s="2">
         <v>4</v>
       </c>
       <c r="D52" s="145" t="s">
-        <v>116</v>
+        <v>141</v>
       </c>
       <c r="E52" s="6"/>
       <c r="F52" s="2">
@@ -5403,7 +5547,7 @@
       <c r="I52" s="75"/>
       <c r="M52" s="122"/>
     </row>
-    <row r="53" spans="2:14" ht="21.6" customHeight="1" thickBot="1" ns3:dyDescent="0.45">
+    <row r="53" spans="2:14" ht="21.6" customHeight="1" thickBot="1">
       <c r="C53" s="2">
         <v>5</v>
       </c>
@@ -5416,7 +5560,7 @@
       <c r="H53" s="75"/>
       <c r="I53" s="75"/>
     </row>
-    <row r="54" spans="2:14" ht="21.6" customHeight="1" thickBot="1" ns3:dyDescent="0.45">
+    <row r="54" spans="2:14" ht="21.6" customHeight="1" thickBot="1">
       <c r="C54" s="2">
         <v>6</v>
       </c>
@@ -5428,7 +5572,7 @@
       <c r="G54" s="109"/>
       <c r="H54" s="109"/>
     </row>
-    <row r="55" spans="2:14" ht="21.6" customHeight="1" thickBot="1" ns3:dyDescent="0.45">
+    <row r="55" spans="2:14" ht="21.6" customHeight="1" thickBot="1">
       <c r="C55" s="2">
         <v>7</v>
       </c>
@@ -5439,10 +5583,10 @@
       <c r="H55" s="66"/>
       <c r="I55" s="66"/>
       <c r="N55" s="9" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="56" spans="2:14" ht="21.6" customHeight="1" ns3:dyDescent="0.4">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="56" spans="2:14" ht="21.6" customHeight="1">
       <c r="C56" s="2"/>
       <c r="D56" s="117"/>
       <c r="F56" s="2"/>
@@ -5450,7 +5594,7 @@
       <c r="H56" s="66"/>
       <c r="I56" s="66"/>
     </row>
-    <row r="57" spans="2:14" ht="21.6" customHeight="1" ns3:dyDescent="0.4">
+    <row r="57" spans="2:14" ht="21.6" customHeight="1">
       <c r="C57" s="1"/>
       <c r="D57" s="66"/>
       <c r="E57" s="66"/>
@@ -5459,25 +5603,25 @@
       <c r="H57" s="66"/>
       <c r="I57" s="66"/>
     </row>
-    <row r="58" spans="2:14" ht="21.6" customHeight="1" thickBot="1" ns3:dyDescent="0.45">
+    <row r="58" spans="2:14" ht="21.6" customHeight="1" thickBot="1">
       <c r="B58" s="4"/>
       <c r="C58" s="4" t="s">
-        <v>71</v>
+        <v>96</v>
       </c>
       <c r="D58" s="110"/>
       <c r="E58" s="5"/>
       <c r="F58" s="4" t="s">
-        <v>72</v>
+        <v>97</v>
       </c>
       <c r="G58" s="110"/>
       <c r="H58" s="110"/>
       <c r="I58" s="110"/>
       <c r="J58" s="4" t="s">
-        <v>73</v>
+        <v>98</v>
       </c>
       <c r="L58" s="111"/>
     </row>
-    <row r="59" spans="2:14" ht="21.6" customHeight="1" ns3:dyDescent="0.4">
+    <row r="59" spans="2:14" ht="21.6" customHeight="1">
       <c r="C59" s="1"/>
       <c r="D59" s="66"/>
       <c r="E59" s="3"/>
@@ -5486,7 +5630,7 @@
       <c r="H59" s="66"/>
       <c r="I59" s="66"/>
     </row>
-    <row r="60" spans="2:14" ht="21.6" customHeight="1" ns3:dyDescent="0.4">
+    <row r="60" spans="2:14" ht="21.6" customHeight="1">
       <c r="C60" s="66"/>
       <c r="D60" s="66"/>
       <c r="E60" s="3"/>
@@ -5495,7 +5639,7 @@
       <c r="H60" s="66"/>
       <c r="I60" s="66"/>
     </row>
-    <row r="61" spans="2:14" ht="21.6" customHeight="1" ns3:dyDescent="0.4">
+    <row r="61" spans="2:14" ht="21.6" customHeight="1">
       <c r="C61" s="66"/>
       <c r="D61" s="66"/>
       <c r="E61" s="66"/>
@@ -5504,19 +5648,19 @@
       <c r="H61" s="66"/>
       <c r="I61" s="66"/>
     </row>
-    <row r="62" spans="2:14" ht="21.6" customHeight="1" ns3:dyDescent="0.4">
+    <row r="62" spans="2:14" ht="21.6" customHeight="1">
       <c r="F62" s="66"/>
       <c r="G62" s="66"/>
       <c r="H62" s="66"/>
       <c r="I62" s="66"/>
     </row>
-    <row r="63" spans="2:14" ht="21.6" customHeight="1" ns3:dyDescent="0.4">
+    <row r="63" spans="2:14" ht="21.6" customHeight="1">
       <c r="F63" s="66"/>
       <c r="G63" s="66"/>
       <c r="H63" s="66"/>
       <c r="I63" s="66"/>
     </row>
-    <row r="64" spans="2:14" ht="21.6" customHeight="1" ns3:dyDescent="0.4">
+    <row r="64" spans="2:14" ht="21.6" customHeight="1">
       <c r="F64" s="66"/>
       <c r="G64" s="66"/>
       <c r="H64" s="66"/>
@@ -5533,7 +5677,7 @@
   <phoneticPr fontId="0" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup scale="75" orientation="landscape" ns4:id="rId1"/>
+  <pageSetup scale="75" orientation="landscape" r:id="rId1"/>
   <headerFooter alignWithMargins="0"/>
 </worksheet>
 </file>

--- a/lineup-template.xlsx
+++ b/lineup-template.xlsx
@@ -2846,6 +2846,9 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65D85805-10C1-44A3-8067-B34748E36517}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:W64"/>
   <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="21.6" customHeight="1"/>
   <cols>
@@ -3982,7 +3985,7 @@
   <phoneticPr fontId="24" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup scale="75" orientation="landscape" r:id="rId1"/>
+  <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="1" r:id="rId1"/>
   <headerFooter alignWithMargins="0"/>
   <drawing r:id="rId2"/>
 </worksheet>

--- a/lineup-template.xlsx
+++ b/lineup-template.xlsx
@@ -1414,7 +1414,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="323">
+  <cellXfs count="379">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1800,15 +1800,17 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
+      <alignment vertical="center" horizontal="center"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf applyAlignment="1" numFmtId="49" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="14" fontId="8" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
+      <alignment vertical="center" horizontal="center"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1817,32 +1819,42 @@
     <xf numFmtId="49" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="18" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyProtection="1">
+    <xf applyAlignment="1" numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf applyAlignment="1" numFmtId="0" fontId="15" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf applyAlignment="1" numFmtId="18" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
+      <alignment vertical="center" horizontal="center"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
+    <xf applyAlignment="1" numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf applyAlignment="1" numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <alignment vertical="center" horizontal="center" wrapText="1"/>
+    </xf>
+    <xf applyAlignment="1" numFmtId="164" fontId="3" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf applyAlignment="1" numFmtId="0" fontId="11" fillId="11" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="11" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1853,19 +1865,24 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf applyAlignment="1" numFmtId="0" fontId="8" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf applyAlignment="1" numFmtId="0" fontId="8" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf applyAlignment="1" numFmtId="0" fontId="23" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+      <alignment vertical="center" horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment vertical="center" horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment vertical="center" horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="11" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1874,41 +1891,44 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="11" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="11" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="12" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment vertical="center" horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="12" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment vertical="center" horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="12" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment vertical="center" horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="12" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment vertical="center" horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="12" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment vertical="center" horizontal="center"/>
     </xf>
     <xf numFmtId="14" fontId="8" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
+      <alignment vertical="center" horizontal="center"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="11" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+    <xf applyAlignment="1" numFmtId="0" fontId="11" fillId="11" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf applyAlignment="1" numFmtId="0" fontId="11" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf applyAlignment="1" numFmtId="0" fontId="11" fillId="11" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="11" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1916,10 +1936,10 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="13" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment vertical="center" horizontal="center"/>
     </xf>
     <xf numFmtId="18" fontId="13" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
+      <alignment vertical="center" horizontal="center"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="13" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1935,40 +1955,45 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf applyAlignment="1" numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment vertical="center" horizontal="center"/>
     </xf>
     <xf numFmtId="49" fontId="8" fillId="0" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment vertical="center" horizontal="center"/>
     </xf>
     <xf numFmtId="49" fontId="8" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment vertical="center" horizontal="center"/>
     </xf>
     <xf numFmtId="49" fontId="8" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment vertical="center" horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="13" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment vertical="center" horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="14" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment vertical="center" horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
+      <alignment vertical="center" horizontal="center"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="18" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="15" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <alignment vertical="center" horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf applyAlignment="1" numFmtId="0" fontId="7" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf applyAlignment="1" numFmtId="0" fontId="7" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2054,8 +2079,8 @@
     </xf>
     <xf numFmtId="164" fontId="34" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="15" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="15" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2073,34 +2098,38 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf applyAlignment="1" numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf applyAlignment="1" numFmtId="0" fontId="3" fillId="15" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="38" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="38" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="16" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="16" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
+      <alignment vertical="center" horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" horizontal="center"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="15" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+      <alignment vertical="center" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2159,36 +2188,36 @@
     <xf numFmtId="164" fontId="3" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment vertical="center" horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="11" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+      <alignment vertical="center" horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment vertical="center" horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment vertical="center" horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment vertical="center" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="38" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="38" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -2256,6 +2285,175 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection locked="0"/>
+    </xf>
+    <xf applyAlignment="1" numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf applyAlignment="1" numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf applyAlignment="1" numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf applyAlignment="1" numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf applyAlignment="1" numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf applyAlignment="1" numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf applyAlignment="1" numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf applyAlignment="1" numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf applyAlignment="1" numFmtId="18" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf applyAlignment="1" numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="18" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center"/>
+    </xf>
+    <xf applyAlignment="1" numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center"/>
+    </xf>
+    <xf applyAlignment="1" numFmtId="49" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf applyAlignment="1" numFmtId="49" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf applyAlignment="1" numFmtId="49" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center"/>
+    </xf>
+    <xf applyAlignment="1" numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf applyAlignment="1" numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center"/>
+    </xf>
+    <xf applyAlignment="1" numFmtId="18" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center"/>
+    </xf>
+    <xf applyAlignment="1" numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center"/>
+    </xf>
+    <xf applyAlignment="1" numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center"/>
+    </xf>
+    <xf applyAlignment="1" numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf applyAlignment="1" numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf applyAlignment="1" numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf applyAlignment="1" numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf applyAlignment="1" numFmtId="0" fontId="16" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf applyAlignment="1" numFmtId="0" fontId="16" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf applyAlignment="1" numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf applyAlignment="1" numFmtId="0" fontId="7" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf applyAlignment="1" numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center"/>
+    </xf>
+    <xf applyAlignment="1" numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2874,31 +3072,31 @@
       <c r="K1" s="291"/>
     </row>
     <row r="2" spans="1:13" ht="21.6" customHeight="1">
-      <c r="B2" s="10"/>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10"/>
+      <c r="B2" s="330"/>
+      <c r="C2" s="330"/>
+      <c r="D2" s="330"/>
       <c r="K2" s="291"/>
     </row>
     <row r="3" spans="1:13" ht="21.6" customHeight="1">
-      <c r="B3" s="10"/>
-      <c r="C3" s="10"/>
-      <c r="D3" s="10"/>
-      <c r="E3" s="10"/>
-      <c r="F3" s="10"/>
-      <c r="G3" s="10"/>
+      <c r="B3" s="330"/>
+      <c r="C3" s="330"/>
+      <c r="D3" s="330"/>
+      <c r="E3" s="330"/>
+      <c r="F3" s="330"/>
+      <c r="G3" s="330"/>
       <c r="K3" s="291"/>
     </row>
     <row r="4" spans="1:13" ht="6.6" customHeight="1">
-      <c r="B4" s="10"/>
-      <c r="C4" s="10"/>
-      <c r="D4" s="10"/>
-      <c r="E4" s="10"/>
-      <c r="F4" s="10"/>
-      <c r="G4" s="10"/>
+      <c r="B4" s="330"/>
+      <c r="C4" s="330"/>
+      <c r="D4" s="330"/>
+      <c r="E4" s="330"/>
+      <c r="F4" s="330"/>
+      <c r="G4" s="330"/>
       <c r="K4" s="291"/>
     </row>
     <row r="5" spans="1:13" ht="37.15" customHeight="1">
-      <c r="A5" s="11"/>
+      <c r="A5" s="331"/>
       <c r="B5" s="292" t="s">
         <v>0</v>
       </c>
@@ -2968,23 +3166,23 @@
       </c>
     </row>
     <row r="8" spans="1:13" ht="21.6" customHeight="1">
-      <c r="A8" s="3"/>
+      <c r="A8" s="325"/>
       <c r="B8" s="156" t="s">
         <v>12</v>
       </c>
-      <c r="C8" s="10"/>
-      <c r="D8" s="10"/>
-      <c r="E8" s="10"/>
-      <c r="F8" s="10"/>
-      <c r="G8" s="10"/>
-      <c r="H8" s="3"/>
-      <c r="I8" s="155" t="s">
+      <c r="C8" s="330"/>
+      <c r="D8" s="330"/>
+      <c r="E8" s="330"/>
+      <c r="F8" s="330"/>
+      <c r="G8" s="330"/>
+      <c r="H8" s="325"/>
+      <c r="I8" s="375" t="s">
         <v>13</v>
       </c>
       <c r="K8" s="260"/>
     </row>
     <row r="9" spans="1:13" ht="21.6" customHeight="1">
-      <c r="B9" s="155" t="s">
+      <c r="B9" s="375" t="s">
         <v>14</v>
       </c>
       <c r="C9" s="298" t="s">
@@ -2992,18 +3190,18 @@
       </c>
       <c r="D9" s="298"/>
       <c r="E9" s="298"/>
-      <c r="F9" s="27"/>
-      <c r="G9" s="28"/>
-      <c r="H9" s="3"/>
-      <c r="I9" s="155" t="s">
+      <c r="F9" s="332"/>
+      <c r="G9" s="333"/>
+      <c r="H9" s="325"/>
+      <c r="I9" s="375" t="s">
         <v>14</v>
       </c>
       <c r="J9" s="257" t="s">
         <v>16</v>
       </c>
       <c r="K9" s="299"/>
-      <c r="L9" s="3"/>
-      <c r="M9" s="30"/>
+      <c r="L9" s="325"/>
+      <c r="M9" s="334"/>
     </row>
     <row r="10" spans="1:13" ht="21.6" customHeight="1">
       <c r="F10" s="167"/>
@@ -3018,18 +3216,18 @@
       <c r="E11" s="179" t="s">
         <v>18</v>
       </c>
-      <c r="F11" s="35"/>
-      <c r="H11" s="28"/>
+      <c r="F11" s="335"/>
+      <c r="H11" s="333"/>
       <c r="I11" s="296" t="s">
         <v>19</v>
       </c>
       <c r="J11" s="296"/>
       <c r="K11" s="259"/>
-      <c r="L11" s="3"/>
-      <c r="M11" s="35"/>
+      <c r="L11" s="325"/>
+      <c r="M11" s="335"/>
     </row>
     <row r="12" spans="1:13" ht="21.6" customHeight="1">
-      <c r="A12" s="36">
+      <c r="A12" s="336">
         <v>1</v>
       </c>
       <c r="B12" s="265" t="s">
@@ -3037,7 +3235,7 @@
       </c>
       <c r="E12" s="206"/>
       <c r="F12" s="205"/>
-      <c r="H12" s="3">
+      <c r="H12" s="325">
         <v>1</v>
       </c>
       <c r="I12" s="213" t="s">
@@ -3045,11 +3243,11 @@
       </c>
       <c r="J12" s="160"/>
       <c r="K12" s="259"/>
-      <c r="L12" s="3"/>
-      <c r="M12" s="35"/>
+      <c r="L12" s="325"/>
+      <c r="M12" s="335"/>
     </row>
     <row r="13" spans="1:13" ht="21.6" customHeight="1">
-      <c r="A13" s="36">
+      <c r="A13" s="336">
         <v>2</v>
       </c>
       <c r="B13" s="265" t="s">
@@ -3057,13 +3255,13 @@
       </c>
       <c r="E13" s="206"/>
       <c r="F13" s="205"/>
-      <c r="H13" s="161"/>
+      <c r="H13" s="377"/>
       <c r="I13" s="162"/>
       <c r="K13" s="259"/>
-      <c r="M13" s="43"/>
+      <c r="M13" s="337"/>
     </row>
     <row r="14" spans="1:13" ht="21.6" customHeight="1">
-      <c r="A14" s="36">
+      <c r="A14" s="336">
         <v>3</v>
       </c>
       <c r="B14" s="266"/>
@@ -3073,10 +3271,10 @@
         <v>23</v>
       </c>
       <c r="K14" s="259"/>
-      <c r="M14" s="43"/>
+      <c r="M14" s="337"/>
     </row>
     <row r="15" spans="1:13" ht="21.6" customHeight="1">
-      <c r="A15" s="36">
+      <c r="A15" s="336">
         <v>4</v>
       </c>
       <c r="B15" s="266"/>
@@ -3089,10 +3287,10 @@
         <v>24</v>
       </c>
       <c r="K15" s="259"/>
-      <c r="M15" s="43"/>
+      <c r="M15" s="337"/>
     </row>
     <row r="16" spans="1:13" ht="21.6" customHeight="1">
-      <c r="A16" s="36">
+      <c r="A16" s="336">
         <v>5</v>
       </c>
       <c r="B16" s="266"/>
@@ -3103,10 +3301,10 @@
       </c>
       <c r="I16" s="163"/>
       <c r="K16" s="259"/>
-      <c r="M16" s="43"/>
+      <c r="M16" s="337"/>
     </row>
     <row r="17" spans="1:23" ht="21.6" customHeight="1">
-      <c r="A17" s="28">
+      <c r="A17" s="333">
         <v>6</v>
       </c>
       <c r="B17" s="266"/>
@@ -3118,12 +3316,12 @@
         <v>25</v>
       </c>
       <c r="K17" s="259"/>
-      <c r="M17" s="43"/>
+      <c r="M17" s="337"/>
     </row>
     <row r="18" spans="1:23" ht="21.6" customHeight="1">
-      <c r="A18" s="48"/>
-      <c r="E18" s="43"/>
-      <c r="F18" s="43"/>
+      <c r="A18" s="338"/>
+      <c r="E18" s="337"/>
+      <c r="F18" s="337"/>
       <c r="H18" s="166">
         <v>1</v>
       </c>
@@ -3131,10 +3329,10 @@
         <v>26</v>
       </c>
       <c r="K18" s="259"/>
-      <c r="M18" s="43"/>
+      <c r="M18" s="337"/>
     </row>
     <row r="19" spans="1:23" ht="21.6" customHeight="1">
-      <c r="A19" s="28"/>
+      <c r="A19" s="333"/>
       <c r="B19" s="293" t="s">
         <v>27</v>
       </c>
@@ -3143,28 +3341,28 @@
       <c r="E19" s="179" t="s">
         <v>18</v>
       </c>
-      <c r="F19" s="51"/>
+      <c r="F19" s="339"/>
       <c r="H19" s="166">
         <v>2</v>
       </c>
       <c r="I19" s="213" t="s">
         <v>28</v>
       </c>
-      <c r="J19" s="3"/>
+      <c r="J19" s="325"/>
       <c r="K19" s="259"/>
-      <c r="L19" s="3"/>
-      <c r="M19" s="35" t="s">
+      <c r="L19" s="325"/>
+      <c r="M19" s="335" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="20" spans="1:23" ht="21.6" customHeight="1">
-      <c r="A20" s="52" t="s">
+      <c r="A20" s="340" t="s">
         <v>30</v>
       </c>
       <c r="B20" s="265" t="s">
         <v>31</v>
       </c>
-      <c r="C20" s="157"/>
+      <c r="C20" s="376"/>
       <c r="E20" s="206"/>
       <c r="F20" s="205"/>
       <c r="I20" s="202" t="s">
@@ -3172,11 +3370,11 @@
       </c>
       <c r="J20" s="170"/>
       <c r="K20" s="259"/>
-      <c r="L20" s="3"/>
-      <c r="M20" s="35"/>
+      <c r="L20" s="325"/>
+      <c r="M20" s="335"/>
     </row>
     <row r="21" spans="1:23" ht="21.6" customHeight="1">
-      <c r="A21" s="56" t="s">
+      <c r="A21" s="341" t="s">
         <v>33</v>
       </c>
       <c r="B21" s="265" t="s">
@@ -3184,7 +3382,7 @@
       </c>
       <c r="E21" s="207"/>
       <c r="F21" s="205"/>
-      <c r="G21" s="9" t="s">
+      <c r="G21" s="329" t="s">
         <v>29</v>
       </c>
       <c r="H21" s="166">
@@ -3195,15 +3393,15 @@
       </c>
       <c r="J21" s="164"/>
       <c r="K21" s="259"/>
-      <c r="L21" s="3"/>
-      <c r="M21" s="35"/>
+      <c r="L21" s="325"/>
+      <c r="M21" s="335"/>
     </row>
     <row r="22" spans="1:23" ht="21.6" customHeight="1">
-      <c r="A22" s="56" t="s">
+      <c r="A22" s="341" t="s">
         <v>36</v>
       </c>
-      <c r="B22" s="115"/>
-      <c r="C22" s="157"/>
+      <c r="B22" s="367"/>
+      <c r="C22" s="376"/>
       <c r="E22" s="208"/>
       <c r="F22" s="205"/>
       <c r="H22" s="166">
@@ -3212,14 +3410,14 @@
       <c r="I22" s="203"/>
       <c r="J22" s="165"/>
       <c r="K22" s="259"/>
-      <c r="L22" s="3"/>
-      <c r="M22" s="35"/>
+      <c r="L22" s="325"/>
+      <c r="M22" s="335"/>
     </row>
     <row r="23" spans="1:23" ht="21.6" customHeight="1">
-      <c r="A23" s="56" t="s">
+      <c r="A23" s="341" t="s">
         <v>37</v>
       </c>
-      <c r="B23" s="115"/>
+      <c r="B23" s="367"/>
       <c r="E23" s="208"/>
       <c r="F23" s="205"/>
       <c r="I23" s="177" t="s">
@@ -3227,19 +3425,19 @@
       </c>
       <c r="J23" s="165"/>
       <c r="K23" s="259"/>
-      <c r="L23" s="3"/>
-      <c r="M23" s="35"/>
-      <c r="W23" s="9" t="s">
+      <c r="L23" s="325"/>
+      <c r="M23" s="335"/>
+      <c r="W23" s="329" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="24" spans="1:23" ht="21.6" customHeight="1">
-      <c r="A24" s="56" t="s">
+      <c r="A24" s="341" t="s">
         <v>39</v>
       </c>
-      <c r="B24" s="115"/>
-      <c r="C24" s="157"/>
-      <c r="D24" s="157"/>
+      <c r="B24" s="367"/>
+      <c r="C24" s="376"/>
+      <c r="D24" s="376"/>
       <c r="E24" s="208"/>
       <c r="F24" s="205"/>
       <c r="H24" s="166">
@@ -3255,9 +3453,9 @@
       <c r="A25" s="158" t="s">
         <v>41</v>
       </c>
-      <c r="B25" s="115"/>
-      <c r="C25" s="157"/>
-      <c r="D25" s="157"/>
+      <c r="B25" s="367"/>
+      <c r="C25" s="376"/>
+      <c r="D25" s="376"/>
       <c r="E25" s="208"/>
       <c r="F25" s="205"/>
       <c r="H25" s="169">
@@ -3270,12 +3468,12 @@
       <c r="K25" s="214"/>
     </row>
     <row r="26" spans="1:23" ht="21.6" customHeight="1">
-      <c r="A26" s="60"/>
-      <c r="B26" s="115"/>
+      <c r="A26" s="342"/>
+      <c r="B26" s="367"/>
       <c r="C26" s="197"/>
       <c r="D26" s="197"/>
-      <c r="E26" s="63"/>
-      <c r="F26" s="157"/>
+      <c r="E26" s="343"/>
+      <c r="F26" s="376"/>
       <c r="H26" s="166">
         <v>3</v>
       </c>
@@ -3284,7 +3482,7 @@
       <c r="K26" s="214"/>
     </row>
     <row r="27" spans="1:23" ht="21.6" customHeight="1">
-      <c r="A27" s="60"/>
+      <c r="A27" s="342"/>
       <c r="B27" s="297" t="s">
         <v>43</v>
       </c>
@@ -3293,12 +3491,12 @@
         <f>C7/(COUNTA(B20:B25))</f>
         <v>28</v>
       </c>
-      <c r="F27" s="77"/>
+      <c r="F27" s="346"/>
       <c r="J27" s="168"/>
       <c r="K27" s="214"/>
     </row>
     <row r="28" spans="1:23" ht="21.6" customHeight="1">
-      <c r="A28" s="60"/>
+      <c r="A28" s="342"/>
       <c r="B28" s="295" t="s">
         <v>44</v>
       </c>
@@ -3307,31 +3505,31 @@
         <f>C7/(COUNTA(B12:B17))</f>
         <v>28</v>
       </c>
-      <c r="F28" s="77"/>
-      <c r="J28" s="66"/>
+      <c r="F28" s="346"/>
+      <c r="J28" s="344"/>
       <c r="K28" s="214"/>
     </row>
     <row r="29" spans="1:23" ht="21.6" customHeight="1">
-      <c r="A29" s="60"/>
-      <c r="F29" s="77"/>
+      <c r="A29" s="342"/>
+      <c r="F29" s="346"/>
       <c r="J29" s="168"/>
       <c r="K29" s="214"/>
     </row>
     <row r="30" spans="1:23" ht="21.6" customHeight="1">
-      <c r="A30" s="60"/>
-      <c r="B30" s="11"/>
-      <c r="C30" s="80"/>
-      <c r="D30" s="80"/>
-      <c r="E30" s="3"/>
-      <c r="F30" s="77"/>
+      <c r="A30" s="342"/>
+      <c r="B30" s="331"/>
+      <c r="C30" s="347"/>
+      <c r="D30" s="347"/>
+      <c r="E30" s="325"/>
+      <c r="F30" s="346"/>
     </row>
     <row r="31" spans="1:23" ht="21.6" customHeight="1">
-      <c r="A31" s="60"/>
-      <c r="B31" s="11"/>
-      <c r="C31" s="80"/>
-      <c r="D31" s="80"/>
-      <c r="E31" s="3"/>
-      <c r="F31" s="77"/>
+      <c r="A31" s="342"/>
+      <c r="B31" s="331"/>
+      <c r="C31" s="347"/>
+      <c r="D31" s="347"/>
+      <c r="E31" s="325"/>
+      <c r="F31" s="346"/>
     </row>
     <row r="33" spans="2:23" ht="21.6" customHeight="1" thickBot="1"/>
     <row r="34" spans="2:23" ht="21.6" customHeight="1" thickBot="1">
@@ -3359,7 +3557,7 @@
       <c r="C35" s="185" t="s">
         <v>48</v>
       </c>
-      <c r="D35" s="7" t="str">
+      <c r="D35" s="328" t="str">
         <f>IF(E35="","",COUNTA($E35:E$35))</f>
         <v/>
       </c>
@@ -3367,29 +3565,29 @@
       <c r="F35" s="187" t="s">
         <v>49</v>
       </c>
-      <c r="G35" s="7" t="str">
+      <c r="G35" s="328" t="str">
         <f>IF(I35="","",(COUNTA($I$35:I35)+COUNTA($E$35:$E$45)))</f>
         <v/>
       </c>
-      <c r="H35" s="87"/>
+      <c r="H35" s="348"/>
       <c r="I35" s="261"/>
-      <c r="K35" s="127" t="s">
+      <c r="K35" s="371" t="s">
         <v>50</v>
       </c>
-      <c r="P35" s="88"/>
-      <c r="Q35" s="88"/>
-      <c r="R35" s="89"/>
-      <c r="S35" s="88"/>
-      <c r="T35" s="88"/>
-      <c r="U35" s="88"/>
-      <c r="V35" s="89"/>
-      <c r="W35" s="88"/>
+      <c r="P35" s="349"/>
+      <c r="Q35" s="349"/>
+      <c r="R35" s="350"/>
+      <c r="S35" s="349"/>
+      <c r="T35" s="349"/>
+      <c r="U35" s="349"/>
+      <c r="V35" s="350"/>
+      <c r="W35" s="349"/>
     </row>
     <row r="36" spans="2:23" ht="21.6" customHeight="1" thickBot="1">
       <c r="C36" s="186" t="s">
         <v>51</v>
       </c>
-      <c r="D36" s="7" t="str">
+      <c r="D36" s="328" t="str">
         <f>IF(E36="","",COUNTA($E$35:E36))</f>
         <v/>
       </c>
@@ -3397,29 +3595,29 @@
       <c r="F36" s="188" t="s">
         <v>52</v>
       </c>
-      <c r="G36" s="7" t="str">
+      <c r="G36" s="328" t="str">
         <f>IF(I36="","",(COUNTA($I$35:I36)+COUNTA($E$35:$E$45)))</f>
         <v/>
       </c>
-      <c r="H36" s="93"/>
+      <c r="H36" s="351"/>
       <c r="I36" s="261"/>
-      <c r="K36" s="94">
+      <c r="K36" s="352">
         <f>COUNTA(I35:I47,E35:E47)</f>
         <v>10</v>
       </c>
-      <c r="P36" s="88"/>
-      <c r="R36" s="95"/>
-      <c r="S36" s="88"/>
-      <c r="T36" s="96"/>
-      <c r="U36" s="96"/>
-      <c r="V36" s="96"/>
-      <c r="W36" s="97"/>
+      <c r="P36" s="349"/>
+      <c r="R36" s="353"/>
+      <c r="S36" s="349"/>
+      <c r="T36" s="354"/>
+      <c r="U36" s="354"/>
+      <c r="V36" s="354"/>
+      <c r="W36" s="355"/>
     </row>
     <row r="37" spans="2:23" ht="21.6" customHeight="1" thickBot="1">
       <c r="C37" s="185" t="s">
         <v>53</v>
       </c>
-      <c r="D37" s="7">
+      <c r="D37" s="328">
         <f>IF(E37="","",COUNTA($E$35:E37))</f>
         <v>1</v>
       </c>
@@ -3429,31 +3627,31 @@
       <c r="F37" s="187" t="s">
         <v>55</v>
       </c>
-      <c r="G37" s="7">
+      <c r="G37" s="328">
         <f>IF(I37="","",(COUNTA($I$35:I37)+COUNTA($E$35:$E$45)))</f>
         <v>6</v>
       </c>
-      <c r="H37" s="93"/>
+      <c r="H37" s="351"/>
       <c r="I37" s="262" t="s">
         <v>56</v>
       </c>
-      <c r="K37" s="130" t="s">
+      <c r="K37" s="372" t="s">
         <v>57</v>
       </c>
-      <c r="P37" s="88"/>
-      <c r="Q37" s="88"/>
-      <c r="R37" s="95"/>
-      <c r="S37" s="88"/>
-      <c r="T37" s="96"/>
-      <c r="U37" s="96"/>
-      <c r="V37" s="96"/>
-      <c r="W37" s="97"/>
+      <c r="P37" s="349"/>
+      <c r="Q37" s="349"/>
+      <c r="R37" s="353"/>
+      <c r="S37" s="349"/>
+      <c r="T37" s="354"/>
+      <c r="U37" s="354"/>
+      <c r="V37" s="354"/>
+      <c r="W37" s="355"/>
     </row>
     <row r="38" spans="2:23" ht="21.6" customHeight="1" thickBot="1">
       <c r="C38" s="186" t="s">
         <v>58</v>
       </c>
-      <c r="D38" s="7" t="str">
+      <c r="D38" s="328" t="str">
         <f>IF(E38="","",COUNTA($E$35:E38))</f>
         <v/>
       </c>
@@ -3461,33 +3659,33 @@
       <c r="F38" s="188" t="s">
         <v>59</v>
       </c>
-      <c r="G38" s="7">
+      <c r="G38" s="328">
         <f>IF(I38="","",(COUNTA($I$35:I38)+COUNTA($E$35:$E$45)))</f>
         <v>7</v>
       </c>
-      <c r="H38" s="93"/>
+      <c r="H38" s="351"/>
       <c r="I38" s="262" t="s">
         <v>60</v>
       </c>
-      <c r="K38" s="294">
+      <c r="K38" s="378">
         <f>C6/K36</f>
         <v>14.3</v>
       </c>
-      <c r="L38" s="294"/>
-      <c r="P38" s="88"/>
-      <c r="Q38" s="88"/>
-      <c r="R38" s="95"/>
-      <c r="S38" s="88"/>
-      <c r="T38" s="96"/>
-      <c r="U38" s="96"/>
-      <c r="V38" s="96"/>
-      <c r="W38" s="97"/>
+      <c r="L38" s="378"/>
+      <c r="P38" s="349"/>
+      <c r="Q38" s="349"/>
+      <c r="R38" s="353"/>
+      <c r="S38" s="349"/>
+      <c r="T38" s="354"/>
+      <c r="U38" s="354"/>
+      <c r="V38" s="354"/>
+      <c r="W38" s="355"/>
     </row>
     <row r="39" spans="2:23" ht="21.6" customHeight="1" thickBot="1">
       <c r="C39" s="185" t="s">
         <v>61</v>
       </c>
-      <c r="D39" s="7" t="str">
+      <c r="D39" s="328" t="str">
         <f>IF(E39="","",COUNTA($E$35:E39))</f>
         <v/>
       </c>
@@ -3495,29 +3693,29 @@
       <c r="F39" s="187" t="s">
         <v>62</v>
       </c>
-      <c r="G39" s="7" t="str">
+      <c r="G39" s="328" t="str">
         <f>IF(I39="","",(COUNTA($I$35:I39)+COUNTA($E$35:$E$45)))</f>
         <v/>
       </c>
-      <c r="H39" s="93"/>
+      <c r="H39" s="351"/>
       <c r="I39" s="261"/>
-      <c r="K39" s="130" t="s">
+      <c r="K39" s="372" t="s">
         <v>63</v>
       </c>
-      <c r="P39" s="88"/>
-      <c r="Q39" s="88"/>
-      <c r="R39" s="95"/>
-      <c r="S39" s="88"/>
-      <c r="T39" s="96"/>
-      <c r="U39" s="96"/>
-      <c r="V39" s="96"/>
-      <c r="W39" s="97"/>
+      <c r="P39" s="349"/>
+      <c r="Q39" s="349"/>
+      <c r="R39" s="353"/>
+      <c r="S39" s="349"/>
+      <c r="T39" s="354"/>
+      <c r="U39" s="354"/>
+      <c r="V39" s="354"/>
+      <c r="W39" s="355"/>
     </row>
     <row r="40" spans="2:23" ht="21.6" customHeight="1">
       <c r="C40" s="186" t="s">
         <v>64</v>
       </c>
-      <c r="D40" s="7">
+      <c r="D40" s="328">
         <f>IF(E40="","",COUNTA($E$35:E40))</f>
         <v>2</v>
       </c>
@@ -3527,30 +3725,30 @@
       <c r="F40" s="188" t="s">
         <v>66</v>
       </c>
-      <c r="G40" s="7" t="str">
+      <c r="G40" s="328" t="str">
         <f>IF(I40="","",(COUNTA($I$35:I40)+COUNTA($E$35:$E$45)))</f>
         <v/>
       </c>
-      <c r="H40" s="93"/>
+      <c r="H40" s="351"/>
       <c r="I40" s="261"/>
-      <c r="K40" s="125">
+      <c r="K40" s="370">
         <f>C7/K36</f>
         <v>5.6</v>
       </c>
-      <c r="P40" s="88"/>
-      <c r="Q40" s="88"/>
-      <c r="R40" s="95"/>
-      <c r="S40" s="88"/>
-      <c r="T40" s="96"/>
-      <c r="U40" s="96"/>
-      <c r="V40" s="96"/>
-      <c r="W40" s="97"/>
+      <c r="P40" s="349"/>
+      <c r="Q40" s="349"/>
+      <c r="R40" s="353"/>
+      <c r="S40" s="349"/>
+      <c r="T40" s="354"/>
+      <c r="U40" s="354"/>
+      <c r="V40" s="354"/>
+      <c r="W40" s="355"/>
     </row>
     <row r="41" spans="2:23" ht="21.6" customHeight="1">
       <c r="C41" s="185" t="s">
         <v>67</v>
       </c>
-      <c r="D41" s="7">
+      <c r="D41" s="328">
         <f>IF(E41="","",COUNTA($E$35:E41))</f>
         <v>3</v>
       </c>
@@ -3560,27 +3758,27 @@
       <c r="F41" s="187" t="s">
         <v>69</v>
       </c>
-      <c r="G41" s="7">
+      <c r="G41" s="328">
         <f>IF(I41="","",(COUNTA($I$35:I41)+COUNTA($E$35:$E$45)))</f>
         <v>8</v>
       </c>
-      <c r="H41" s="93"/>
+      <c r="H41" s="351"/>
       <c r="I41" s="262" t="s">
         <v>70</v>
       </c>
-      <c r="P41" s="88"/>
-      <c r="R41" s="95"/>
-      <c r="S41" s="96"/>
-      <c r="T41" s="96"/>
-      <c r="U41" s="96"/>
-      <c r="V41" s="96"/>
-      <c r="W41" s="97"/>
+      <c r="P41" s="349"/>
+      <c r="R41" s="353"/>
+      <c r="S41" s="354"/>
+      <c r="T41" s="354"/>
+      <c r="U41" s="354"/>
+      <c r="V41" s="354"/>
+      <c r="W41" s="355"/>
     </row>
     <row r="42" spans="2:23" ht="21.6" customHeight="1">
       <c r="C42" s="186" t="s">
         <v>71</v>
       </c>
-      <c r="D42" s="7">
+      <c r="D42" s="328">
         <f>IF(E42="","",COUNTA($E$35:E42))</f>
         <v>4</v>
       </c>
@@ -3590,29 +3788,29 @@
       <c r="F42" s="188" t="s">
         <v>73</v>
       </c>
-      <c r="G42" s="7">
+      <c r="G42" s="328">
         <f>IF(I42="","",(COUNTA($I$35:I42)+COUNTA($E$35:$E$45)))</f>
         <v>9</v>
       </c>
-      <c r="H42" s="93"/>
+      <c r="H42" s="351"/>
       <c r="I42" s="262" t="s">
         <v>74</v>
       </c>
       <c r="K42" s="204"/>
-      <c r="P42" s="88"/>
-      <c r="Q42" s="88"/>
-      <c r="R42" s="95"/>
-      <c r="S42" s="96"/>
-      <c r="T42" s="96"/>
-      <c r="U42" s="96"/>
-      <c r="V42" s="96"/>
-      <c r="W42" s="97"/>
+      <c r="P42" s="349"/>
+      <c r="Q42" s="349"/>
+      <c r="R42" s="353"/>
+      <c r="S42" s="354"/>
+      <c r="T42" s="354"/>
+      <c r="U42" s="354"/>
+      <c r="V42" s="354"/>
+      <c r="W42" s="355"/>
     </row>
     <row r="43" spans="2:23" ht="21.6" customHeight="1">
       <c r="C43" s="185" t="s">
         <v>75</v>
       </c>
-      <c r="D43" s="7">
+      <c r="D43" s="328">
         <f>IF(E43="","",COUNTA($E$35:E43))</f>
         <v>5</v>
       </c>
@@ -3622,29 +3820,29 @@
       <c r="F43" s="187" t="s">
         <v>77</v>
       </c>
-      <c r="G43" s="7" t="str">
+      <c r="G43" s="328" t="str">
         <f>IF(I43="","",(COUNTA($I$35:I43)+COUNTA($E$35:$E$45)))</f>
         <v/>
       </c>
-      <c r="H43" s="93"/>
+      <c r="H43" s="351"/>
       <c r="I43" s="261"/>
-      <c r="P43" s="88"/>
-      <c r="Q43" s="88"/>
-      <c r="R43" s="95"/>
-      <c r="S43" s="96"/>
-      <c r="T43" s="96"/>
-      <c r="U43" s="96"/>
-      <c r="V43" s="96"/>
-      <c r="W43" s="97"/>
+      <c r="P43" s="349"/>
+      <c r="Q43" s="349"/>
+      <c r="R43" s="353"/>
+      <c r="S43" s="354"/>
+      <c r="T43" s="354"/>
+      <c r="U43" s="354"/>
+      <c r="V43" s="354"/>
+      <c r="W43" s="355"/>
     </row>
     <row r="44" spans="2:23" ht="21.6" customHeight="1">
-      <c r="B44" s="9" t="s">
+      <c r="B44" s="329" t="s">
         <v>29</v>
       </c>
       <c r="C44" s="186" t="s">
         <v>78</v>
       </c>
-      <c r="D44" s="7" t="str">
+      <c r="D44" s="328" t="str">
         <f>IF(E44="","",COUNTA($E$35:E44))</f>
         <v/>
       </c>
@@ -3652,29 +3850,29 @@
       <c r="F44" s="188" t="s">
         <v>79</v>
       </c>
-      <c r="G44" s="7">
+      <c r="G44" s="328">
         <f>IF(I44="","",(COUNTA($I$35:I44)+COUNTA($E$35:$E$45)))</f>
         <v>10</v>
       </c>
-      <c r="H44" s="93"/>
+      <c r="H44" s="351"/>
       <c r="I44" s="262" t="s">
         <v>80</v>
       </c>
-      <c r="P44" s="88"/>
-      <c r="Q44" s="88"/>
-      <c r="R44" s="95"/>
-      <c r="S44" s="96"/>
-      <c r="T44" s="96"/>
-      <c r="U44" s="96"/>
-      <c r="V44" s="96"/>
-      <c r="W44" s="97"/>
+      <c r="P44" s="349"/>
+      <c r="Q44" s="349"/>
+      <c r="R44" s="353"/>
+      <c r="S44" s="354"/>
+      <c r="T44" s="354"/>
+      <c r="U44" s="354"/>
+      <c r="V44" s="354"/>
+      <c r="W44" s="355"/>
     </row>
     <row r="45" spans="2:23" ht="21.6" customHeight="1">
-      <c r="B45" s="98"/>
+      <c r="B45" s="356"/>
       <c r="C45" s="185" t="s">
         <v>81</v>
       </c>
-      <c r="D45" s="7" t="str">
+      <c r="D45" s="328" t="str">
         <f>IF(E45="","",COUNTA($E$35:E45))</f>
         <v/>
       </c>
@@ -3682,26 +3880,26 @@
       <c r="F45" s="189" t="s">
         <v>82</v>
       </c>
-      <c r="G45" s="7" t="str">
+      <c r="G45" s="328" t="str">
         <f>IF(I45="","",(COUNTA($I$35:I45)+COUNTA($E$35:$E$45)))</f>
         <v/>
       </c>
-      <c r="H45" s="93"/>
+      <c r="H45" s="351"/>
       <c r="I45" s="211"/>
-      <c r="P45" s="88"/>
-      <c r="Q45" s="88"/>
-      <c r="R45" s="95"/>
-      <c r="S45" s="100"/>
-      <c r="T45" s="96"/>
-      <c r="U45" s="96"/>
-      <c r="V45" s="96"/>
-      <c r="W45" s="97"/>
+      <c r="P45" s="349"/>
+      <c r="Q45" s="349"/>
+      <c r="R45" s="353"/>
+      <c r="S45" s="357"/>
+      <c r="T45" s="354"/>
+      <c r="U45" s="354"/>
+      <c r="V45" s="354"/>
+      <c r="W45" s="355"/>
     </row>
     <row r="46" spans="2:23" ht="21.6" customHeight="1">
-      <c r="C46" s="101" t="s">
+      <c r="C46" s="358" t="s">
         <v>83</v>
       </c>
-      <c r="D46" s="7" t="str">
+      <c r="D46" s="328" t="str">
         <f>IF(E46="","",COUNTA($E$36:E46))</f>
         <v/>
       </c>
@@ -3709,60 +3907,60 @@
       <c r="F46" s="189" t="s">
         <v>84</v>
       </c>
-      <c r="G46" s="7" t="str">
+      <c r="G46" s="328" t="str">
         <f>IF(I46="","",(COUNTA($I$35:I46)+COUNTA($E$35:$E$45)))</f>
         <v/>
       </c>
-      <c r="H46" s="103"/>
+      <c r="H46" s="359"/>
       <c r="I46" s="211"/>
-      <c r="P46" s="88"/>
-      <c r="Q46" s="88"/>
-      <c r="R46" s="95"/>
-      <c r="S46" s="96"/>
-      <c r="T46" s="96"/>
-      <c r="U46" s="96"/>
-      <c r="V46" s="96"/>
-      <c r="W46" s="97"/>
+      <c r="P46" s="349"/>
+      <c r="Q46" s="349"/>
+      <c r="R46" s="353"/>
+      <c r="S46" s="354"/>
+      <c r="T46" s="354"/>
+      <c r="U46" s="354"/>
+      <c r="V46" s="354"/>
+      <c r="W46" s="355"/>
     </row>
     <row r="47" spans="2:23" thickBot="1">
-      <c r="C47" s="104"/>
-      <c r="D47" s="7" t="str">
+      <c r="C47" s="360"/>
+      <c r="D47" s="328" t="str">
         <f>IF(E47="","",COUNTA($E$36:E47))</f>
         <v/>
       </c>
-      <c r="E47" s="118"/>
+      <c r="E47" s="368"/>
       <c r="F47" s="189" t="s">
         <v>85</v>
       </c>
-      <c r="G47" s="7" t="str">
+      <c r="G47" s="328" t="str">
         <f>IF(I47="","",(COUNTA($I$35:I47)+COUNTA($E$35:$E$45)))</f>
         <v/>
       </c>
-      <c r="H47" s="105"/>
+      <c r="H47" s="361"/>
       <c r="I47" s="211"/>
       <c r="J47" s="210" t="s">
         <v>86</v>
       </c>
-      <c r="K47" s="3"/>
-      <c r="P47" s="88"/>
-      <c r="Q47" s="88"/>
-      <c r="R47" s="95"/>
-      <c r="S47" s="96"/>
-      <c r="T47" s="96"/>
-      <c r="U47" s="96"/>
-      <c r="V47" s="96"/>
-      <c r="W47" s="96"/>
+      <c r="K47" s="325"/>
+      <c r="P47" s="349"/>
+      <c r="Q47" s="349"/>
+      <c r="R47" s="353"/>
+      <c r="S47" s="354"/>
+      <c r="T47" s="354"/>
+      <c r="U47" s="354"/>
+      <c r="V47" s="354"/>
+      <c r="W47" s="354"/>
     </row>
     <row r="48" spans="2:23" ht="21.6" customHeight="1" thickBot="1">
-      <c r="C48" s="107" t="s">
+      <c r="C48" s="362" t="s">
         <v>87</v>
       </c>
-      <c r="D48" s="107"/>
-      <c r="F48" s="107" t="s">
+      <c r="D48" s="362"/>
+      <c r="F48" s="362" t="s">
         <v>88</v>
       </c>
-      <c r="G48" s="108"/>
-      <c r="H48" s="108"/>
+      <c r="G48" s="363"/>
+      <c r="H48" s="363"/>
       <c r="I48" s="153"/>
       <c r="J48" s="209" t="s">
         <v>89</v>
@@ -3772,203 +3970,203 @@
       </c>
     </row>
     <row r="49" spans="2:13" ht="21.6" customHeight="1" thickBot="1">
-      <c r="C49" s="9">
+      <c r="C49" s="329">
         <v>1</v>
       </c>
       <c r="E49" s="263" t="s">
         <v>91</v>
       </c>
-      <c r="G49" s="9" t="s">
+      <c r="G49" s="329" t="s">
         <v>92</v>
       </c>
       <c r="J49" s="264">
         <v>152</v>
       </c>
-      <c r="K49" s="9">
+      <c r="K49" s="329">
         <f>COUNTA(E49:E60)</f>
         <v>4</v>
       </c>
     </row>
     <row r="50" spans="2:13" ht="21.6" customHeight="1" thickBot="1">
-      <c r="C50" s="2">
+      <c r="C50" s="324">
         <v>2</v>
       </c>
-      <c r="D50" s="2"/>
+      <c r="D50" s="324"/>
       <c r="E50" s="263" t="s">
         <v>35</v>
       </c>
-      <c r="F50" s="2">
+      <c r="F50" s="324">
         <v>1</v>
       </c>
-      <c r="G50" s="75"/>
-      <c r="H50" s="75"/>
-      <c r="I50" s="75"/>
+      <c r="G50" s="345"/>
+      <c r="H50" s="345"/>
+      <c r="I50" s="345"/>
       <c r="K50" s="199" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="51" spans="2:13" ht="21.6" customHeight="1">
-      <c r="C51" s="2">
+      <c r="C51" s="324">
         <v>3</v>
       </c>
-      <c r="D51" s="2"/>
+      <c r="D51" s="324"/>
       <c r="E51" s="263" t="s">
         <v>93</v>
       </c>
-      <c r="F51" s="2">
+      <c r="F51" s="324">
         <v>2</v>
       </c>
-      <c r="G51" s="75"/>
-      <c r="H51" s="75"/>
-      <c r="I51" s="75"/>
-      <c r="K51" s="133">
+      <c r="G51" s="345"/>
+      <c r="H51" s="345"/>
+      <c r="I51" s="345"/>
+      <c r="K51" s="373">
         <f>J49/K49</f>
         <v>38</v>
       </c>
     </row>
     <row r="52" spans="2:13" ht="21.6" customHeight="1">
-      <c r="C52" s="2">
+      <c r="C52" s="324">
         <v>4</v>
       </c>
-      <c r="D52" s="2"/>
+      <c r="D52" s="324"/>
       <c r="E52" s="263" t="s">
         <v>94</v>
       </c>
-      <c r="F52" s="2">
+      <c r="F52" s="324">
         <v>3</v>
       </c>
-      <c r="G52" s="75"/>
-      <c r="H52" s="75"/>
-      <c r="I52" s="75"/>
-      <c r="L52" s="122"/>
+      <c r="G52" s="345"/>
+      <c r="H52" s="345"/>
+      <c r="I52" s="345"/>
+      <c r="L52" s="369"/>
     </row>
     <row r="53" spans="2:13" ht="21.6" customHeight="1">
-      <c r="C53" s="2">
+      <c r="C53" s="324">
         <v>5</v>
       </c>
-      <c r="D53" s="2"/>
+      <c r="D53" s="324"/>
       <c r="E53" s="211"/>
-      <c r="F53" s="2">
+      <c r="F53" s="324">
         <v>4</v>
       </c>
-      <c r="G53" s="75"/>
-      <c r="H53" s="75"/>
-      <c r="I53" s="75"/>
+      <c r="G53" s="345"/>
+      <c r="H53" s="345"/>
+      <c r="I53" s="345"/>
     </row>
     <row r="54" spans="2:13" ht="21.6" customHeight="1" thickBot="1">
-      <c r="C54" s="2">
+      <c r="C54" s="324">
         <v>6</v>
       </c>
-      <c r="D54" s="2"/>
+      <c r="D54" s="324"/>
       <c r="E54" s="211"/>
-      <c r="F54" s="2">
+      <c r="F54" s="324">
         <v>5</v>
       </c>
-      <c r="G54" s="109"/>
-      <c r="H54" s="109"/>
-      <c r="I54" s="109"/>
+      <c r="G54" s="364"/>
+      <c r="H54" s="364"/>
+      <c r="I54" s="364"/>
     </row>
     <row r="55" spans="2:13" ht="21.6" customHeight="1">
-      <c r="C55" s="2">
+      <c r="C55" s="324">
         <v>7</v>
       </c>
-      <c r="D55" s="2"/>
-      <c r="E55" s="138"/>
-      <c r="F55" s="3"/>
-      <c r="G55" s="66"/>
-      <c r="H55" s="66"/>
-      <c r="I55" s="66"/>
-      <c r="M55" s="9" t="s">
+      <c r="D55" s="324"/>
+      <c r="E55" s="374"/>
+      <c r="F55" s="325"/>
+      <c r="G55" s="344"/>
+      <c r="H55" s="344"/>
+      <c r="I55" s="344"/>
+      <c r="M55" s="329" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="56" spans="2:13" ht="21.6" customHeight="1">
-      <c r="C56" s="2"/>
-      <c r="D56" s="2"/>
-      <c r="E56" s="138"/>
-      <c r="F56" s="2"/>
-      <c r="G56" s="66"/>
-      <c r="H56" s="66"/>
-      <c r="I56" s="66"/>
+      <c r="C56" s="324"/>
+      <c r="D56" s="324"/>
+      <c r="E56" s="374"/>
+      <c r="F56" s="324"/>
+      <c r="G56" s="344"/>
+      <c r="H56" s="344"/>
+      <c r="I56" s="344"/>
     </row>
     <row r="57" spans="2:13" ht="21.6" customHeight="1">
-      <c r="C57" s="1"/>
-      <c r="D57" s="1"/>
-      <c r="E57" s="66"/>
-      <c r="F57" s="66"/>
-      <c r="G57" s="66"/>
-      <c r="H57" s="66"/>
-      <c r="I57" s="66"/>
+      <c r="C57" s="323"/>
+      <c r="D57" s="323"/>
+      <c r="E57" s="344"/>
+      <c r="F57" s="344"/>
+      <c r="G57" s="344"/>
+      <c r="H57" s="344"/>
+      <c r="I57" s="344"/>
     </row>
     <row r="58" spans="2:13" ht="21.6" customHeight="1" thickBot="1">
-      <c r="B58" s="4"/>
-      <c r="C58" s="4" t="s">
+      <c r="B58" s="326"/>
+      <c r="C58" s="326" t="s">
         <v>96</v>
       </c>
-      <c r="D58" s="4"/>
-      <c r="E58" s="5"/>
-      <c r="F58" s="4" t="s">
+      <c r="D58" s="326"/>
+      <c r="E58" s="327"/>
+      <c r="F58" s="326" t="s">
         <v>97</v>
       </c>
-      <c r="G58" s="110"/>
-      <c r="H58" s="110"/>
-      <c r="I58" s="110"/>
-      <c r="J58" s="4" t="s">
+      <c r="G58" s="365"/>
+      <c r="H58" s="365"/>
+      <c r="I58" s="365"/>
+      <c r="J58" s="326" t="s">
         <v>98</v>
       </c>
-      <c r="K58" s="111"/>
+      <c r="K58" s="366"/>
     </row>
     <row r="59" spans="2:13" ht="21.6" customHeight="1">
-      <c r="C59" s="1"/>
-      <c r="D59" s="1"/>
-      <c r="E59" s="3"/>
-      <c r="F59" s="66"/>
-      <c r="G59" s="66"/>
-      <c r="H59" s="66"/>
-      <c r="I59" s="66"/>
+      <c r="C59" s="323"/>
+      <c r="D59" s="323"/>
+      <c r="E59" s="325"/>
+      <c r="F59" s="344"/>
+      <c r="G59" s="344"/>
+      <c r="H59" s="344"/>
+      <c r="I59" s="344"/>
     </row>
     <row r="60" spans="2:13" ht="21.6" customHeight="1">
-      <c r="C60" s="66"/>
-      <c r="D60" s="66"/>
-      <c r="E60" s="3"/>
-      <c r="F60" s="66"/>
-      <c r="G60" s="66"/>
-      <c r="H60" s="66"/>
-      <c r="I60" s="66"/>
+      <c r="C60" s="344"/>
+      <c r="D60" s="344"/>
+      <c r="E60" s="325"/>
+      <c r="F60" s="344"/>
+      <c r="G60" s="344"/>
+      <c r="H60" s="344"/>
+      <c r="I60" s="344"/>
     </row>
     <row r="61" spans="2:13" ht="21.6" customHeight="1">
-      <c r="C61" s="66"/>
-      <c r="D61" s="66"/>
-      <c r="E61" s="66"/>
-      <c r="F61" s="66"/>
-      <c r="G61" s="66"/>
-      <c r="H61" s="66"/>
-      <c r="I61" s="66"/>
+      <c r="C61" s="344"/>
+      <c r="D61" s="344"/>
+      <c r="E61" s="344"/>
+      <c r="F61" s="344"/>
+      <c r="G61" s="344"/>
+      <c r="H61" s="344"/>
+      <c r="I61" s="344"/>
     </row>
     <row r="62" spans="2:13" ht="21.6" customHeight="1">
-      <c r="F62" s="66"/>
-      <c r="G62" s="66"/>
-      <c r="H62" s="66"/>
-      <c r="I62" s="66"/>
-      <c r="K62" s="9">
+      <c r="F62" s="344"/>
+      <c r="G62" s="344"/>
+      <c r="H62" s="344"/>
+      <c r="I62" s="344"/>
+      <c r="K62" s="329">
         <f>COUNTA(E49:E60)</f>
         <v>4</v>
       </c>
     </row>
     <row r="63" spans="2:13" ht="21.6" customHeight="1">
-      <c r="F63" s="66"/>
-      <c r="G63" s="66"/>
-      <c r="H63" s="66"/>
-      <c r="I63" s="66"/>
+      <c r="F63" s="344"/>
+      <c r="G63" s="344"/>
+      <c r="H63" s="344"/>
+      <c r="I63" s="344"/>
     </row>
     <row r="64" spans="2:13" ht="21.6" customHeight="1">
-      <c r="F64" s="66"/>
-      <c r="G64" s="66"/>
-      <c r="H64" s="66"/>
-      <c r="I64" s="66"/>
+      <c r="F64" s="344"/>
+      <c r="G64" s="344"/>
+      <c r="H64" s="344"/>
+      <c r="I64" s="344"/>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="1"/>
+  <sheetProtection selectLockedCells="323"/>
   <dataConsolidate link="1"/>
   <mergeCells count="10">
     <mergeCell ref="K1:K5"/>
@@ -3985,7 +4183,7 @@
   <phoneticPr fontId="24" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="1" r:id="rId1"/>
+  <pageSetup orientation="portrait" fitToWidth="1" fitToHeight="1" r:id="rId1"/>
   <headerFooter alignWithMargins="0"/>
   <drawing r:id="rId2"/>
 </worksheet>

--- a/lineup-template.xlsx
+++ b/lineup-template.xlsx
@@ -503,7 +503,7 @@
     </font>
     <font>
       <i/>
-      <sz val="11"/>
+      <sz val="13"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -512,7 +512,7 @@
     <font>
       <b/>
       <i/>
-      <sz val="16"/>
+      <sz val="18"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -520,14 +520,14 @@
     </font>
     <font>
       <b/>
-      <sz val="16"/>
+      <sz val="18"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <i/>
-      <sz val="16"/>
+      <sz val="18"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -535,67 +535,27 @@
     </font>
     <font>
       <i/>
-      <sz val="16"/>
+      <sz val="18"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <i/>
-      <sz val="12"/>
+      <sz val="14"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="16"/>
+      <sz val="18"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="14"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="20"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="14"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <u/>
       <sz val="16"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -609,7 +569,47 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
+      <b/>
+      <sz val="14"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="22"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="18"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -633,7 +633,7 @@
     </font>
     <font>
       <b/>
-      <sz val="16"/>
+      <sz val="18"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -641,7 +641,7 @@
     </font>
     <font>
       <b/>
-      <sz val="12"/>
+      <sz val="14"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -649,14 +649,14 @@
     </font>
     <font>
       <b/>
-      <sz val="16"/>
+      <sz val="18"/>
       <color theme="0"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="12"/>
+      <sz val="14"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -665,7 +665,7 @@
     <font>
       <b/>
       <i/>
-      <sz val="14"/>
+      <sz val="16"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -753,7 +753,7 @@
     </font>
     <font>
       <i/>
-      <sz val="14"/>
+      <sz val="16"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>

--- a/lineup-template.xlsx
+++ b/lineup-template.xlsx
@@ -3054,11 +3054,11 @@
     <col min="2" max="2" width="14.28515625" style="9" customWidth="1"/>
     <col min="3" max="3" width="13.140625" style="9" customWidth="1"/>
     <col min="4" max="4" width="12.7109375" style="9" customWidth="1"/>
-    <col min="5" max="5" width="15.140625" style="9" customWidth="1"/>
+    <col min="5" max="5" width="20.140625" style="9" customWidth="1"/>
     <col min="6" max="6" width="13" style="9" customWidth="1"/>
     <col min="7" max="7" width="12.7109375" style="9" customWidth="1"/>
     <col min="8" max="8" width="2.140625" style="9" customWidth="1"/>
-    <col min="9" max="9" width="16.140625" style="9" customWidth="1"/>
+    <col min="9" max="9" width="21.140625" style="9" customWidth="1"/>
     <col min="10" max="10" width="16.42578125" style="9" customWidth="1"/>
     <col min="11" max="11" width="61.7109375" style="9" customWidth="1"/>
     <col min="12" max="12" width="1" style="9" customWidth="1"/>
